--- a/Aii竞彩推荐_2026-05-09.xlsx
+++ b/Aii竞彩推荐_2026-05-09.xlsx
@@ -83,12 +83,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF9C4"/>
+        <fgColor rgb="00C8E6C9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C8E6C9"/>
+        <fgColor rgb="00FFF9C4"/>
       </patternFill>
     </fill>
     <fill>
@@ -192,10 +192,13 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -204,13 +207,10 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -614,7 +614,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：中国竞彩网(sporttery)+500.com · 21:04</t>
+          <t>数据来源：中国竞彩网(sporttery)+500.com · 22:44</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>SP3.53/3.40/1.81 让球+1</t>
+          <t>SP3.40/3.40/1.85 让球+1</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>SP1.92/2.93/3.75 让球-1</t>
+          <t>SP1.80/2.90/4.40 让球-1</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>SP1.79/3.60/3.42 让球-1</t>
+          <t>SP1.76/3.60/3.53 让球-1</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>SP3.70/3.40/1.77 让球+1</t>
+          <t>SP3.57/3.30/1.83 让球+1</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>SP5.00/5.00/1.37 让球+1</t>
+          <t>SP4.70/4.95/1.40 让球+1</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1857,7 @@
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>SP1.90/3.35/3.28 让球-1</t>
+          <t>SP1.87/3.35/3.38 让球-1</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>SP3.94/4.05/1.59 让球0</t>
+          <t>SP4.18/4.15/1.54 让球0</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>SP6.00/4.90/1.32 让球0</t>
+          <t>SP6.50/5.15/1.28 让球0</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>SP2.05/3.50/2.81 让球-1</t>
+          <t>SP2.09/3.27/2.90 让球-1</t>
         </is>
       </c>
     </row>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>SP7.00/4.16/1.34 让球+1</t>
+          <t>SP6.90/4.30/1.33 让球+1</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>📊 竞彩SP数据（含真实让球SP · 21:04）</t>
+          <t>📊 竞彩SP数据（含真实让球SP · 22:44）</t>
         </is>
       </c>
     </row>
@@ -2954,13 +2954,13 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>3.53</v>
+        <v>3.4</v>
       </c>
       <c r="E62" s="7" t="n">
         <v>3.4</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
@@ -2969,17 +2969,17 @@
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.52</t>
         </is>
       </c>
     </row>
@@ -3046,13 +3046,13 @@
         </is>
       </c>
       <c r="D64" s="7" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="F64" s="7" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
@@ -3061,17 +3061,17 @@
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.80</t>
         </is>
       </c>
     </row>
@@ -3092,13 +3092,13 @@
         </is>
       </c>
       <c r="D65" s="6" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="E65" s="6" t="n">
         <v>3.6</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>3.42</v>
+        <v>3.53</v>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
@@ -3107,17 +3107,17 @@
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.80</t>
         </is>
       </c>
     </row>
@@ -3138,13 +3138,13 @@
         </is>
       </c>
       <c r="D66" s="7" t="n">
-        <v>3.7</v>
+        <v>3.57</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
@@ -3153,17 +3153,17 @@
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="I66" s="7" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="J66" s="7" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.56</t>
         </is>
       </c>
     </row>
@@ -3230,13 +3230,13 @@
         </is>
       </c>
       <c r="D68" s="7" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="F68" s="7" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="I68" s="7" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.10</t>
         </is>
       </c>
     </row>
@@ -3276,13 +3276,13 @@
         </is>
       </c>
       <c r="D69" s="6" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="E69" s="6" t="n">
         <v>3.35</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>3.28</v>
+        <v>3.38</v>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
@@ -3291,17 +3291,17 @@
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.73</t>
         </is>
       </c>
     </row>
@@ -3322,32 +3322,32 @@
         </is>
       </c>
       <c r="D70" s="7" t="n">
-        <v>3.94</v>
+        <v>4.18</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="F70" s="7" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H70" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I70" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J70" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="I70" s="7" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="J70" s="7" t="inlineStr">
+        <is>
+          <t>2.62</t>
         </is>
       </c>
     </row>
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="D71" s="6" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="E71" s="6" t="n">
-        <v>4.9</v>
+        <v>5.15</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
@@ -3383,17 +3383,17 @@
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.94</t>
         </is>
       </c>
     </row>
@@ -3414,32 +3414,32 @@
         </is>
       </c>
       <c r="D72" s="7" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="E72" s="7" t="n">
-        <v>3.5</v>
+        <v>3.27</v>
       </c>
       <c r="F72" s="7" t="n">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="H72" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I72" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J72" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
+      <c r="H72" s="7" t="inlineStr">
+        <is>
+          <t>4.45</t>
+        </is>
+      </c>
+      <c r="I72" s="7" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="J72" s="7" t="inlineStr">
+        <is>
+          <t>1.55</t>
         </is>
       </c>
     </row>
@@ -3460,13 +3460,13 @@
         </is>
       </c>
       <c r="D73" s="6" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="E73" s="6" t="n">
-        <v>4.16</v>
+        <v>4.3</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="J73" s="6" t="inlineStr">
@@ -3640,7 +3640,7 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J80" s="9" t="inlineStr">
+      <c r="J80" s="8" t="inlineStr">
         <is>
           <t>贝叶斯P主=159%P平=100%P客=97%|泊松比分1-0|半全场胜胜|大小球小2.5(44%)|让球-1=输盘/让平/让负</t>
         </is>
@@ -3692,7 +3692,7 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J81" s="9" t="inlineStr">
+      <c r="J81" s="8" t="inlineStr">
         <is>
           <t>贝叶斯P主=223%P平=93%P客=77%|泊松比分2-0|半全场胜胜|大小球小2.5(45%)|让球-1=输盘/让平/让负</t>
         </is>
@@ -3744,7 +3744,7 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J82" s="9" t="inlineStr">
+      <c r="J82" s="8" t="inlineStr">
         <is>
           <t>贝叶斯P主=58%P平=85%P客=235%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球+1=输盘/让平/让负</t>
         </is>
@@ -3796,111 +3796,111 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J83" s="9" t="inlineStr">
+      <c r="J83" s="8" t="inlineStr">
         <is>
           <t>贝叶斯P主=141%P平=90%P客=73%|泊松比分1-0|半全场胜胜|大小球小2.5(44%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="10" t="inlineStr">
+      <c r="A84" s="9" t="inlineStr">
         <is>
           <t>周六005</t>
         </is>
       </c>
-      <c r="B84" s="10" t="inlineStr">
+      <c r="B84" s="9" t="inlineStr">
         <is>
           <t>波鸿vs汉诺威96</t>
         </is>
       </c>
-      <c r="C84" s="10" t="inlineStr">
+      <c r="C84" s="9" t="inlineStr">
         <is>
           <t>客胜</t>
         </is>
       </c>
-      <c r="D84" s="10" t="inlineStr">
+      <c r="D84" s="9" t="inlineStr">
         <is>
           <t>7/10</t>
         </is>
       </c>
-      <c r="E84" s="10" t="inlineStr">
+      <c r="E84" s="9" t="inlineStr">
         <is>
           <t>1-2</t>
         </is>
       </c>
-      <c r="F84" s="10" t="inlineStr">
+      <c r="F84" s="9" t="inlineStr">
         <is>
           <t>1-3</t>
         </is>
       </c>
-      <c r="G84" s="10" t="inlineStr">
+      <c r="G84" s="9" t="inlineStr">
         <is>
           <t>负负</t>
         </is>
       </c>
-      <c r="H84" s="10" t="inlineStr">
+      <c r="H84" s="9" t="inlineStr">
         <is>
           <t>平负</t>
         </is>
       </c>
-      <c r="I84" s="10" t="inlineStr">
+      <c r="I84" s="9" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="J84" s="11" t="inlineStr">
+      <c r="J84" s="10" t="inlineStr">
         <is>
           <t>贝叶斯P主=98%P平=96%P客=211%|泊松比分1-2|半全场负负|大小球大2.5(70%)|让球+1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="10" t="inlineStr">
+      <c r="A85" s="9" t="inlineStr">
         <is>
           <t>周六006</t>
         </is>
       </c>
-      <c r="B85" s="10" t="inlineStr">
+      <c r="B85" s="9" t="inlineStr">
         <is>
           <t>利物浦vs切尔西</t>
         </is>
       </c>
-      <c r="C85" s="10" t="inlineStr">
+      <c r="C85" s="9" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="D85" s="10" t="inlineStr">
+      <c r="D85" s="9" t="inlineStr">
         <is>
           <t>7/10</t>
         </is>
       </c>
-      <c r="E85" s="10" t="inlineStr">
+      <c r="E85" s="9" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="F85" s="10" t="inlineStr">
+      <c r="F85" s="9" t="inlineStr">
         <is>
           <t>3-1</t>
         </is>
       </c>
-      <c r="G85" s="10" t="inlineStr">
+      <c r="G85" s="9" t="inlineStr">
         <is>
           <t>胜胜</t>
         </is>
       </c>
-      <c r="H85" s="10" t="inlineStr">
+      <c r="H85" s="9" t="inlineStr">
         <is>
           <t>平胜</t>
         </is>
       </c>
-      <c r="I85" s="10" t="inlineStr">
+      <c r="I85" s="9" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="J85" s="11" t="inlineStr">
+      <c r="J85" s="10" t="inlineStr">
         <is>
           <t>贝叶斯P主=199%P平=100%P客=113%|泊松比分2-1|半全场胜胜|大小球大2.5(70%)|让球-1=输盘/让平/让负</t>
         </is>
@@ -3952,7 +3952,7 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J86" s="9" t="inlineStr">
+      <c r="J86" s="8" t="inlineStr">
         <is>
           <t>贝叶斯P主=153%P平=100%P客=91%|泊松比分3-1|半全场胜胜|大小球大2.5(71%)|让球-1=输盘/让平/让负</t>
         </is>
@@ -4004,59 +4004,59 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J87" s="9" t="inlineStr">
+      <c r="J87" s="8" t="inlineStr">
         <is>
           <t>贝叶斯P主=159%P平=100%P客=102%|泊松比分2-1|半全场胜胜|大小球大2.5(67%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="10" t="inlineStr">
+      <c r="A88" s="9" t="inlineStr">
         <is>
           <t>周六009</t>
         </is>
       </c>
-      <c r="B88" s="10" t="inlineStr">
+      <c r="B88" s="9" t="inlineStr">
         <is>
           <t>萨普斯堡vs腓特烈</t>
         </is>
       </c>
-      <c r="C88" s="10" t="inlineStr">
+      <c r="C88" s="9" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="D88" s="10" t="inlineStr">
+      <c r="D88" s="9" t="inlineStr">
         <is>
           <t>7/10</t>
         </is>
       </c>
-      <c r="E88" s="10" t="inlineStr">
+      <c r="E88" s="9" t="inlineStr">
         <is>
           <t>1-0</t>
         </is>
       </c>
-      <c r="F88" s="10" t="inlineStr">
+      <c r="F88" s="9" t="inlineStr">
         <is>
           <t>2-0</t>
         </is>
       </c>
-      <c r="G88" s="10" t="inlineStr">
+      <c r="G88" s="9" t="inlineStr">
         <is>
           <t>胜胜</t>
         </is>
       </c>
-      <c r="H88" s="10" t="inlineStr">
+      <c r="H88" s="9" t="inlineStr">
         <is>
           <t>平胜</t>
         </is>
       </c>
-      <c r="I88" s="10" t="inlineStr">
+      <c r="I88" s="9" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="J88" s="11" t="inlineStr">
+      <c r="J88" s="10" t="inlineStr">
         <is>
           <t>贝叶斯P主=199%P平=100%P客=113%|泊松比分1-0|半全场胜胜|大小球小2.5(44%)|让球-1=输盘/让平/让负</t>
         </is>
@@ -4108,54 +4108,54 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J89" s="9" t="inlineStr">
+      <c r="J89" s="8" t="inlineStr">
         <is>
           <t>贝叶斯P主=265%P平=89%P客=59%|泊松比分2-0|半全场胜胜|大小球小2.5(43%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="8" t="inlineStr">
+      <c r="A90" s="11" t="inlineStr">
         <is>
           <t>周六011</t>
         </is>
       </c>
-      <c r="B90" s="8" t="inlineStr">
+      <c r="B90" s="11" t="inlineStr">
         <is>
           <t>卡利亚里vs乌迪内斯</t>
         </is>
       </c>
-      <c r="C90" s="8" t="inlineStr">
+      <c r="C90" s="11" t="inlineStr">
         <is>
           <t>平局</t>
         </is>
       </c>
-      <c r="D90" s="8" t="inlineStr">
+      <c r="D90" s="11" t="inlineStr">
         <is>
           <t>5/10</t>
         </is>
       </c>
-      <c r="E90" s="8" t="inlineStr">
+      <c r="E90" s="11" t="inlineStr">
         <is>
           <t>2-2</t>
         </is>
       </c>
-      <c r="F90" s="8" t="inlineStr">
+      <c r="F90" s="11" t="inlineStr">
         <is>
           <t>1-2</t>
         </is>
       </c>
-      <c r="G90" s="8" t="inlineStr">
+      <c r="G90" s="11" t="inlineStr">
         <is>
           <t>平平</t>
         </is>
       </c>
-      <c r="H90" s="8" t="inlineStr">
+      <c r="H90" s="11" t="inlineStr">
         <is>
           <t>平负</t>
         </is>
       </c>
-      <c r="I90" s="8" t="inlineStr">
+      <c r="I90" s="11" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
@@ -4167,52 +4167,52 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="10" t="inlineStr">
+      <c r="A91" s="9" t="inlineStr">
         <is>
           <t>周六012</t>
         </is>
       </c>
-      <c r="B91" s="10" t="inlineStr">
+      <c r="B91" s="9" t="inlineStr">
         <is>
           <t>代格福什vs米亚尔比</t>
         </is>
       </c>
-      <c r="C91" s="10" t="inlineStr">
+      <c r="C91" s="9" t="inlineStr">
         <is>
           <t>客胜</t>
         </is>
       </c>
-      <c r="D91" s="10" t="inlineStr">
+      <c r="D91" s="9" t="inlineStr">
         <is>
           <t>7/10</t>
         </is>
       </c>
-      <c r="E91" s="10" t="inlineStr">
+      <c r="E91" s="9" t="inlineStr">
         <is>
           <t>0-1</t>
         </is>
       </c>
-      <c r="F91" s="10" t="inlineStr">
+      <c r="F91" s="9" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="G91" s="10" t="inlineStr">
+      <c r="G91" s="9" t="inlineStr">
         <is>
           <t>平负</t>
         </is>
       </c>
-      <c r="H91" s="10" t="inlineStr">
+      <c r="H91" s="9" t="inlineStr">
         <is>
           <t>负负</t>
         </is>
       </c>
-      <c r="I91" s="10" t="inlineStr">
+      <c r="I91" s="9" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="J91" s="11" t="inlineStr">
+      <c r="J91" s="10" t="inlineStr">
         <is>
           <t>贝叶斯P主=91%P平=100%P客=168%|泊松比分0-1|半全场平负|大小球小2.5(42%)|让球+1=输盘/让平/让负</t>
         </is>
@@ -4264,59 +4264,59 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J92" s="9" t="inlineStr">
+      <c r="J92" s="8" t="inlineStr">
         <is>
           <t>贝叶斯P主=77%P平=90%P客=262%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球+1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="10" t="inlineStr">
+      <c r="A93" s="9" t="inlineStr">
         <is>
           <t>周六014</t>
         </is>
       </c>
-      <c r="B93" s="10" t="inlineStr">
+      <c r="B93" s="9" t="inlineStr">
         <is>
           <t>奥格斯堡vs门兴</t>
         </is>
       </c>
-      <c r="C93" s="10" t="inlineStr">
+      <c r="C93" s="9" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="D93" s="10" t="inlineStr">
+      <c r="D93" s="9" t="inlineStr">
         <is>
           <t>7/10</t>
         </is>
       </c>
-      <c r="E93" s="10" t="inlineStr">
+      <c r="E93" s="9" t="inlineStr">
         <is>
           <t>3-2</t>
         </is>
       </c>
-      <c r="F93" s="10" t="inlineStr">
+      <c r="F93" s="9" t="inlineStr">
         <is>
           <t>2-3</t>
         </is>
       </c>
-      <c r="G93" s="10" t="inlineStr">
+      <c r="G93" s="9" t="inlineStr">
         <is>
           <t>胜胜</t>
         </is>
       </c>
-      <c r="H93" s="10" t="inlineStr">
+      <c r="H93" s="9" t="inlineStr">
         <is>
           <t>平胜</t>
         </is>
       </c>
-      <c r="I93" s="10" t="inlineStr">
+      <c r="I93" s="9" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="J93" s="11" t="inlineStr">
+      <c r="J93" s="10" t="inlineStr">
         <is>
           <t>贝叶斯P主=211%P平=98%P客=111%|泊松比分3-2|半全场负负|大小球大2.5(72%)|让球-1=输盘/让平/让负</t>
         </is>
@@ -4368,7 +4368,7 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J94" s="9" t="inlineStr">
+      <c r="J94" s="8" t="inlineStr">
         <is>
           <t>贝叶斯P主=297%P平=79%P客=66%|泊松比分3-2|半全场胜胜|大小球大2.5(72%)|让球-1=输盘/让平/让负</t>
         </is>
@@ -4420,113 +4420,113 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J95" s="9" t="inlineStr">
+      <c r="J95" s="8" t="inlineStr">
         <is>
           <t>贝叶斯P主=185%P平=98%P客=137%|泊松比分3-2|半全场负负|大小球大2.5(72%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="10" t="inlineStr">
+      <c r="A96" s="9" t="inlineStr">
         <is>
           <t>周六017</t>
         </is>
       </c>
-      <c r="B96" s="10" t="inlineStr">
+      <c r="B96" s="9" t="inlineStr">
         <is>
           <t>莱红牛vs圣保利</t>
         </is>
       </c>
-      <c r="C96" s="10" t="inlineStr">
+      <c r="C96" s="9" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="D96" s="10" t="inlineStr">
+      <c r="D96" s="9" t="inlineStr">
         <is>
           <t>9/10</t>
         </is>
       </c>
-      <c r="E96" s="10" t="inlineStr">
+      <c r="E96" s="9" t="inlineStr">
         <is>
           <t>3-1</t>
         </is>
       </c>
-      <c r="F96" s="10" t="inlineStr">
+      <c r="F96" s="9" t="inlineStr">
         <is>
           <t>3-2</t>
         </is>
       </c>
-      <c r="G96" s="10" t="inlineStr">
+      <c r="G96" s="9" t="inlineStr">
         <is>
           <t>胜胜</t>
         </is>
       </c>
-      <c r="H96" s="10" t="inlineStr">
+      <c r="H96" s="9" t="inlineStr">
         <is>
           <t>平胜</t>
         </is>
       </c>
-      <c r="I96" s="10" t="inlineStr">
+      <c r="I96" s="9" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="J96" s="11" t="inlineStr">
+      <c r="J96" s="10" t="inlineStr">
         <is>
           <t>贝叶斯P主=336%P平=71%P客=44%|泊松比分3-1|半全场胜胜|大小球大2.5(71%)|让球-2=输盘/让平/让负⚠️让-2深盘·主胜可能不穿盘</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="10" t="inlineStr">
+      <c r="A97" s="9" t="inlineStr">
         <is>
           <t>周六018</t>
         </is>
       </c>
-      <c r="B97" s="10" t="inlineStr">
+      <c r="B97" s="9" t="inlineStr">
         <is>
           <t>桑德兰vs曼联</t>
         </is>
       </c>
-      <c r="C97" s="10" t="inlineStr">
+      <c r="C97" s="9" t="inlineStr">
         <is>
           <t>客胜</t>
         </is>
       </c>
-      <c r="D97" s="10" t="inlineStr">
+      <c r="D97" s="9" t="inlineStr">
         <is>
           <t>7/10</t>
         </is>
       </c>
-      <c r="E97" s="10" t="inlineStr">
+      <c r="E97" s="9" t="inlineStr">
         <is>
           <t>1-2</t>
         </is>
       </c>
-      <c r="F97" s="10" t="inlineStr">
+      <c r="F97" s="9" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="G97" s="10" t="inlineStr">
+      <c r="G97" s="9" t="inlineStr">
         <is>
           <t>负负</t>
         </is>
       </c>
-      <c r="H97" s="10" t="inlineStr">
+      <c r="H97" s="9" t="inlineStr">
         <is>
           <t>平负</t>
         </is>
       </c>
-      <c r="I97" s="10" t="inlineStr">
+      <c r="I97" s="9" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="J97" s="11" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=96%P平=100%P客=188%|泊松比分1-2|半全场胜胜|大小球大2.5(69%)|让球+1=输盘/让平/让负</t>
+      <c r="J97" s="10" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=100%P平=100%P客=184%|泊松比分1-2|半全场胜胜|大小球大2.5(69%)|让球+1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -4576,215 +4576,215 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J98" s="9" t="inlineStr">
+      <c r="J98" s="8" t="inlineStr">
         <is>
           <t>贝叶斯P主=118%P平=100%P客=140%|泊松比分1-3|半全场负负|大小球大2.5(69%)|让球+1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="6" t="inlineStr">
+      <c r="A99" s="9" t="inlineStr">
         <is>
           <t>周六020</t>
         </is>
       </c>
-      <c r="B99" s="6" t="inlineStr">
+      <c r="B99" s="9" t="inlineStr">
         <is>
           <t>塞维利亚vs西班牙人</t>
         </is>
       </c>
-      <c r="C99" s="6" t="inlineStr">
+      <c r="C99" s="9" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="D99" s="6" t="inlineStr">
-        <is>
-          <t>5/10</t>
-        </is>
-      </c>
-      <c r="E99" s="6" t="inlineStr">
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>7/10</t>
+        </is>
+      </c>
+      <c r="E99" s="9" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="F99" s="6" t="inlineStr">
+      <c r="F99" s="9" t="inlineStr">
         <is>
           <t>1-2</t>
         </is>
       </c>
-      <c r="G99" s="6" t="inlineStr">
+      <c r="G99" s="9" t="inlineStr">
         <is>
           <t>胜胜</t>
         </is>
       </c>
-      <c r="H99" s="6" t="inlineStr">
+      <c r="H99" s="9" t="inlineStr">
         <is>
           <t>平胜</t>
         </is>
       </c>
-      <c r="I99" s="6" t="inlineStr">
+      <c r="I99" s="9" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="J99" s="9" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=137%P平=90%P客=70%|泊松比分2-1|半全场负负|大小球大2.5(70%)|让球-1=输盘/让平/让负</t>
+      <c r="J99" s="10" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=145%P平=90%P客=59%|泊松比分2-1|半全场负负|大小球大2.5(70%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="10" t="inlineStr">
+      <c r="A100" s="9" t="inlineStr">
         <is>
           <t>周六021</t>
         </is>
       </c>
-      <c r="B100" s="10" t="inlineStr">
+      <c r="B100" s="9" t="inlineStr">
         <is>
           <t>威廉二世vs瓦尔韦克</t>
         </is>
       </c>
-      <c r="C100" s="10" t="inlineStr">
+      <c r="C100" s="9" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="D100" s="10" t="inlineStr">
+      <c r="D100" s="9" t="inlineStr">
         <is>
           <t>7/10</t>
         </is>
       </c>
-      <c r="E100" s="10" t="inlineStr">
+      <c r="E100" s="9" t="inlineStr">
         <is>
           <t>2-0</t>
         </is>
       </c>
-      <c r="F100" s="10" t="inlineStr">
+      <c r="F100" s="9" t="inlineStr">
         <is>
           <t>1-0</t>
         </is>
       </c>
-      <c r="G100" s="10" t="inlineStr">
+      <c r="G100" s="9" t="inlineStr">
         <is>
           <t>胜胜</t>
         </is>
       </c>
-      <c r="H100" s="10" t="inlineStr">
+      <c r="H100" s="9" t="inlineStr">
         <is>
           <t>平胜</t>
         </is>
       </c>
-      <c r="I100" s="10" t="inlineStr">
+      <c r="I100" s="9" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="J100" s="11" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=201%P平=100%P客=105%|泊松比分2-0|半全场胜胜|大小球小2.5(46%)|让球-1=输盘/让平/让负</t>
+      <c r="J100" s="10" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=205%P平=100%P客=102%|泊松比分2-0|半全场胜胜|大小球小2.5(46%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="10" t="inlineStr">
+      <c r="A101" s="9" t="inlineStr">
         <is>
           <t>周六022</t>
         </is>
       </c>
-      <c r="B101" s="10" t="inlineStr">
+      <c r="B101" s="9" t="inlineStr">
         <is>
           <t>拉齐奥vs国际米兰</t>
         </is>
       </c>
-      <c r="C101" s="10" t="inlineStr">
+      <c r="C101" s="9" t="inlineStr">
         <is>
           <t>客胜</t>
         </is>
       </c>
-      <c r="D101" s="10" t="inlineStr">
+      <c r="D101" s="9" t="inlineStr">
         <is>
           <t>7/10</t>
         </is>
       </c>
-      <c r="E101" s="10" t="inlineStr">
+      <c r="E101" s="9" t="inlineStr">
         <is>
           <t>1-3</t>
         </is>
       </c>
-      <c r="F101" s="10" t="inlineStr">
+      <c r="F101" s="9" t="inlineStr">
         <is>
           <t>1-2</t>
         </is>
       </c>
-      <c r="G101" s="10" t="inlineStr">
+      <c r="G101" s="9" t="inlineStr">
         <is>
           <t>负负</t>
         </is>
       </c>
-      <c r="H101" s="10" t="inlineStr">
+      <c r="H101" s="9" t="inlineStr">
         <is>
           <t>平负</t>
         </is>
       </c>
-      <c r="I101" s="10" t="inlineStr">
+      <c r="I101" s="9" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="J101" s="11" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=87%P平=95%P客=182%|泊松比分1-3|半全场负负|大小球大2.5(70%)|让球+1=输盘/让平/让负</t>
+      <c r="J101" s="10" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=90%P平=97%P客=175%|泊松比分1-3|半全场负负|大小球大2.5(70%)|让球+1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="10" t="inlineStr">
+      <c r="A102" s="9" t="inlineStr">
         <is>
           <t>周六023</t>
         </is>
       </c>
-      <c r="B102" s="10" t="inlineStr">
+      <c r="B102" s="9" t="inlineStr">
         <is>
           <t>曼城vs布伦特</t>
         </is>
       </c>
-      <c r="C102" s="10" t="inlineStr">
+      <c r="C102" s="9" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="D102" s="10" t="inlineStr">
+      <c r="D102" s="9" t="inlineStr">
         <is>
           <t>9/10</t>
         </is>
       </c>
-      <c r="E102" s="10" t="inlineStr">
+      <c r="E102" s="9" t="inlineStr">
         <is>
           <t>4-1</t>
         </is>
       </c>
-      <c r="F102" s="10" t="inlineStr">
+      <c r="F102" s="9" t="inlineStr">
         <is>
           <t>3-1</t>
         </is>
       </c>
-      <c r="G102" s="10" t="inlineStr">
+      <c r="G102" s="9" t="inlineStr">
         <is>
           <t>胜胜</t>
         </is>
       </c>
-      <c r="H102" s="10" t="inlineStr">
+      <c r="H102" s="9" t="inlineStr">
         <is>
           <t>平胜</t>
         </is>
       </c>
-      <c r="I102" s="10" t="inlineStr">
+      <c r="I102" s="9" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="J102" s="11" t="inlineStr">
+      <c r="J102" s="10" t="inlineStr">
         <is>
           <t>贝叶斯P主=324%P平=72%P客=53%|泊松比分4-1|半全场胜胜|大小球大2.5(72%)|让球-1=输盘/让平/让负</t>
         </is>
@@ -4836,61 +4836,61 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J103" s="9" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=78%P平=78%P客=286%|泊松比分1-4|半全场负负|大小球大2.5(73%)|让球+1=输盘/让平/让负</t>
+      <c r="J103" s="8" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=83%P平=79%P客=280%|泊松比分1-4|半全场负负|大小球大2.5(73%)|让球+1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="10" t="inlineStr">
+      <c r="A104" s="9" t="inlineStr">
         <is>
           <t>周六025</t>
         </is>
       </c>
-      <c r="B104" s="10" t="inlineStr">
+      <c r="B104" s="9" t="inlineStr">
         <is>
           <t>马竞vs塞尔塔</t>
         </is>
       </c>
-      <c r="C104" s="10" t="inlineStr">
+      <c r="C104" s="9" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="D104" s="10" t="inlineStr">
+      <c r="D104" s="9" t="inlineStr">
         <is>
           <t>7/10</t>
         </is>
       </c>
-      <c r="E104" s="10" t="inlineStr">
+      <c r="E104" s="9" t="inlineStr">
         <is>
           <t>3-1</t>
         </is>
       </c>
-      <c r="F104" s="10" t="inlineStr">
+      <c r="F104" s="9" t="inlineStr">
         <is>
           <t>4-1</t>
         </is>
       </c>
-      <c r="G104" s="10" t="inlineStr">
+      <c r="G104" s="9" t="inlineStr">
         <is>
           <t>胜胜</t>
         </is>
       </c>
-      <c r="H104" s="10" t="inlineStr">
+      <c r="H104" s="9" t="inlineStr">
         <is>
           <t>平胜</t>
         </is>
       </c>
-      <c r="I104" s="10" t="inlineStr">
+      <c r="I104" s="9" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="J104" s="11" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=176%P平=100%P客=102%|泊松比分3-1|半全场胜胜|大小球大2.5(71%)|让球-1=输盘/让平/让负</t>
+      <c r="J104" s="10" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=179%P平=100%P客=99%|泊松比分3-1|半全场胜胜|大小球大2.5(71%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -4922,79 +4922,79 @@
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
+          <t>负负</t>
+        </is>
+      </c>
+      <c r="H105" s="6" t="inlineStr">
+        <is>
           <t>平负</t>
         </is>
       </c>
-      <c r="H105" s="6" t="inlineStr">
+      <c r="I105" s="6" t="inlineStr">
+        <is>
+          <t>2元</t>
+        </is>
+      </c>
+      <c r="J105" s="8" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=97%P平=98%P客=263%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球0=无让球/—</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="9" t="inlineStr">
+        <is>
+          <t>周六027</t>
+        </is>
+      </c>
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t>迈季宽广vs胡巴卡德</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="inlineStr">
+        <is>
+          <t>9/10</t>
+        </is>
+      </c>
+      <c r="E106" s="9" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="F106" s="9" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="G106" s="9" t="inlineStr">
         <is>
           <t>负负</t>
         </is>
       </c>
-      <c r="I105" s="6" t="inlineStr">
+      <c r="H106" s="9" t="inlineStr">
+        <is>
+          <t>平负</t>
+        </is>
+      </c>
+      <c r="I106" s="9" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="J105" s="9" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=102%P平=99%P客=253%|泊松比分0-1|半全场平负|大小球小2.5(41%)|让球0=无让球/—</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="10" t="inlineStr">
-        <is>
-          <t>周六027</t>
-        </is>
-      </c>
-      <c r="B106" s="10" t="inlineStr">
-        <is>
-          <t>迈季宽广vs胡巴卡德</t>
-        </is>
-      </c>
-      <c r="C106" s="10" t="inlineStr">
-        <is>
-          <t>客胜</t>
-        </is>
-      </c>
-      <c r="D106" s="10" t="inlineStr">
-        <is>
-          <t>9/10</t>
-        </is>
-      </c>
-      <c r="E106" s="10" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="F106" s="10" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="G106" s="10" t="inlineStr">
-        <is>
-          <t>负负</t>
-        </is>
-      </c>
-      <c r="H106" s="10" t="inlineStr">
-        <is>
-          <t>平负</t>
-        </is>
-      </c>
-      <c r="I106" s="10" t="inlineStr">
-        <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="J106" s="11" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=75%P平=92%P客=342%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球0=无让球/—</t>
+      <c r="J106" s="10" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=70%P平=88%P客=356%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -5044,9 +5044,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J107" s="9" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=151%P平=88%P客=110%|泊松比分1-0|半全场平胜|大小球小2.5(41%)|让球-1=输盘/让平/让负</t>
+      <c r="J107" s="8" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=145%P平=93%P客=105%|泊松比分1-0|半全场平胜|大小球小2.5(41%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -5096,9 +5096,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J108" s="9" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=48%P平=81%P客=252%|泊松比分1-2|半全场负负|大小球大2.5(69%)|让球+1=输盘/让平/让负</t>
+      <c r="J108" s="8" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=49%P平=79%P客=255%|泊松比分1-2|半全场负负|大小球大2.5(69%)|让球+1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
@@ -5214,100 +5214,100 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="10" t="n">
+      <c r="A115" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B115" s="10" t="inlineStr">
+      <c r="B115" s="9" t="inlineStr">
         <is>
           <t>周六017</t>
         </is>
       </c>
-      <c r="C115" s="10" t="inlineStr">
+      <c r="C115" s="9" t="inlineStr">
         <is>
           <t>德甲</t>
         </is>
       </c>
-      <c r="D115" s="10" t="inlineStr">
+      <c r="D115" s="9" t="inlineStr">
         <is>
           <t>莱红牛</t>
         </is>
       </c>
-      <c r="E115" s="10" t="inlineStr">
+      <c r="E115" s="9" t="inlineStr">
         <is>
           <t>圣保利</t>
         </is>
       </c>
-      <c r="F115" s="10" t="inlineStr">
+      <c r="F115" s="9" t="inlineStr">
         <is>
           <t>1.19/5.65/9.00</t>
         </is>
       </c>
-      <c r="G115" s="10" t="inlineStr">
+      <c r="G115" s="9" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="H115" s="10" t="inlineStr">
+      <c r="H115" s="9" t="inlineStr">
         <is>
           <t>9/10</t>
         </is>
       </c>
-      <c r="I115" s="10" t="inlineStr">
+      <c r="I115" s="9" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="J115" s="10" t="inlineStr">
+      <c r="J115" s="9" t="inlineStr">
         <is>
           <t>让-2深盘·主胜可能不穿盘</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="10" t="n">
+      <c r="A116" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B116" s="10" t="inlineStr">
+      <c r="B116" s="9" t="inlineStr">
         <is>
           <t>周六023</t>
         </is>
       </c>
-      <c r="C116" s="10" t="inlineStr">
+      <c r="C116" s="9" t="inlineStr">
         <is>
           <t>英超</t>
         </is>
       </c>
-      <c r="D116" s="10" t="inlineStr">
+      <c r="D116" s="9" t="inlineStr">
         <is>
           <t>曼城</t>
         </is>
       </c>
-      <c r="E116" s="10" t="inlineStr">
+      <c r="E116" s="9" t="inlineStr">
         <is>
           <t>布伦特</t>
         </is>
       </c>
-      <c r="F116" s="10" t="inlineStr">
+      <c r="F116" s="9" t="inlineStr">
         <is>
           <t>1.23/5.50/7.45</t>
         </is>
       </c>
-      <c r="G116" s="10" t="inlineStr">
+      <c r="G116" s="9" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="H116" s="10" t="inlineStr">
+      <c r="H116" s="9" t="inlineStr">
         <is>
           <t>9/10</t>
         </is>
       </c>
-      <c r="I116" s="10" t="inlineStr">
+      <c r="I116" s="9" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="J116" s="10" t="inlineStr">
+      <c r="J116" s="9" t="inlineStr">
         <is>
           <t>让-1盘</t>
         </is>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>6.00/4.90/1.32</t>
+          <t>6.50/5.15/1.28</t>
         </is>
       </c>
       <c r="G117" s="6" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="F123" s="6" t="inlineStr">
         <is>
-          <t>3.53/3.40/1.81</t>
+          <t>3.40/3.40/1.85</t>
         </is>
       </c>
       <c r="G123" s="6" t="inlineStr">
@@ -5669,27 +5669,27 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>周六021</t>
+          <t>周六020</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>荷乙</t>
+          <t>西甲</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>威廉二世</t>
+          <t>塞维利亚</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
-          <t>瓦尔韦克</t>
+          <t>西班牙人</t>
         </is>
       </c>
       <c r="F124" s="6" t="inlineStr">
         <is>
-          <t>1.79/3.60/3.42</t>
+          <t>1.80/2.90/4.40</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr">
@@ -5719,32 +5719,32 @@
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>周六022</t>
+          <t>周六021</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>意甲</t>
+          <t>荷乙</t>
         </is>
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>拉齐奥</t>
+          <t>威廉二世</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>国际米兰</t>
+          <t>瓦尔韦克</t>
         </is>
       </c>
       <c r="F125" s="6" t="inlineStr">
         <is>
-          <t>3.70/3.40/1.77</t>
+          <t>1.76/3.60/3.53</t>
         </is>
       </c>
       <c r="G125" s="6" t="inlineStr">
         <is>
-          <t>客胜/平局</t>
+          <t>主胜/平局</t>
         </is>
       </c>
       <c r="H125" s="6" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="J125" s="6" t="inlineStr">
         <is>
-          <t>让+1盘</t>
+          <t>让-1盘</t>
         </is>
       </c>
     </row>
@@ -5769,32 +5769,32 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>周六025</t>
+          <t>周六022</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>意甲</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>马竞</t>
+          <t>拉齐奥</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
         <is>
-          <t>塞尔塔</t>
+          <t>国际米兰</t>
         </is>
       </c>
       <c r="F126" s="6" t="inlineStr">
         <is>
-          <t>1.90/3.35/3.28</t>
+          <t>3.57/3.30/1.83</t>
         </is>
       </c>
       <c r="G126" s="6" t="inlineStr">
         <is>
-          <t>主胜/平局</t>
+          <t>客胜/平局</t>
         </is>
       </c>
       <c r="H126" s="6" t="inlineStr">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="J126" s="6" t="inlineStr">
         <is>
-          <t>让-1盘</t>
+          <t>让+1盘</t>
         </is>
       </c>
     </row>
@@ -5819,27 +5819,27 @@
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>周六001</t>
+          <t>周六025</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>澳超</t>
+          <t>西甲</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>奥克兰FC</t>
+          <t>马竞</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>阿德莱德</t>
+          <t>塞尔塔</t>
         </is>
       </c>
       <c r="F127" s="6" t="inlineStr">
         <is>
-          <t>1.98/3.15/3.26</t>
+          <t>1.87/3.35/3.38</t>
         </is>
       </c>
       <c r="G127" s="6" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="H127" s="6" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>7/10</t>
         </is>
       </c>
       <c r="I127" s="6" t="inlineStr">
@@ -5869,27 +5869,27 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>周六004</t>
+          <t>周六001</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>韩职</t>
+          <t>澳超</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>大田市民</t>
+          <t>奥克兰FC</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
         <is>
-          <t>浦项制铁</t>
+          <t>阿德莱德</t>
         </is>
       </c>
       <c r="F128" s="6" t="inlineStr">
         <is>
-          <t>1.91/3.00/3.68</t>
+          <t>1.98/3.15/3.26</t>
         </is>
       </c>
       <c r="G128" s="6" t="inlineStr">
@@ -6031,7 +6031,7 @@
           <t>周六017+周六023</t>
         </is>
       </c>
-      <c r="C150" s="9" t="inlineStr">
+      <c r="C150" s="8" t="inlineStr">
         <is>
           <t>·莱红牛:主胜(1.19)
 ·曼城:主胜(1.23)</t>
@@ -6067,11 +6067,11 @@
           <t>周六017+周六023+周六027</t>
         </is>
       </c>
-      <c r="C151" s="9" t="inlineStr">
+      <c r="C151" s="8" t="inlineStr">
         <is>
           <t>·莱红牛:主胜(1.19)
 ·曼城:主胜(1.23)
-·迈季宽广:客胜(1.32)</t>
+·迈季宽广:客胜(1.28)</t>
         </is>
       </c>
       <c r="D151" s="6" t="n">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="F151" s="6" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="G151" s="6" t="inlineStr">
         <is>
-          <t>1.19×1.23×1.32=1.93</t>
+          <t>1.19×1.23×1.28=1.87</t>
         </is>
       </c>
     </row>
@@ -6104,11 +6104,11 @@
           <t>周六017+周六023+周六027+周六005</t>
         </is>
       </c>
-      <c r="C152" s="9" t="inlineStr">
+      <c r="C152" s="8" t="inlineStr">
         <is>
           <t>·莱红牛:主胜(1.19)
 ·曼城:主胜(1.23)
-·迈季宽广:客胜(1.32)
+·迈季宽广:客胜(1.28)
 ·波鸿:客胜(1.70)</t>
         </is>
       </c>
@@ -6122,12 +6122,12 @@
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="G152" s="6" t="inlineStr">
         <is>
-          <t>1.19×1.23×1.32×1.70=3.28</t>
+          <t>1.19×1.23×1.28×1.70=3.19</t>
         </is>
       </c>
     </row>
@@ -6142,11 +6142,11 @@
           <t>周六017+周六023+周六027+周六005+周六006</t>
         </is>
       </c>
-      <c r="C153" s="9" t="inlineStr">
+      <c r="C153" s="8" t="inlineStr">
         <is>
           <t>·莱红牛:主胜(1.19)
 ·曼城:主胜(1.23)
-·迈季宽广:客胜(1.32)
+·迈季宽广:客胜(1.28)
 ·波鸿:客胜(1.70)
 ·利物浦:主胜(1.83)</t>
         </is>
@@ -6161,12 +6161,12 @@
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="G153" s="6" t="inlineStr">
         <is>
-          <t>1.19×1.23×1.32×1.70×1.83=6.01</t>
+          <t>1.19×1.23×1.28×1.70×1.83=5.83</t>
         </is>
       </c>
     </row>
@@ -6181,11 +6181,11 @@
           <t>周六017+周六023+周六027+周六005+周六006+周六009</t>
         </is>
       </c>
-      <c r="C154" s="9" t="inlineStr">
+      <c r="C154" s="8" t="inlineStr">
         <is>
           <t>·莱红牛:主胜(1.19)
 ·曼城:主胜(1.23)
-·迈季宽广:客胜(1.32)
+·迈季宽广:客胜(1.28)
 ·波鸿:客胜(1.70)
 ·利物浦:主胜(1.83)
 ·萨普斯堡:主胜(1.83)</t>
@@ -6201,12 +6201,12 @@
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>11.00</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="G154" s="6" t="inlineStr">
         <is>
-          <t>1.19×1.23×1.32×1.70×1.83×1.83=11.00</t>
+          <t>1.19×1.23×1.28×1.70×1.83×1.83=10.67</t>
         </is>
       </c>
     </row>
@@ -6240,7 +6240,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="10" t="inlineStr">
+      <c r="A160" s="9" t="inlineStr">
         <is>
           <t>🟢 高信心(7/10+)</t>
         </is>
@@ -6262,7 +6262,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="10" t="inlineStr">
+      <c r="A161" s="9" t="inlineStr">
         <is>
           <t>🟢 让球SP真实数据</t>
         </is>
@@ -6284,7 +6284,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="8" t="inlineStr">
+      <c r="A162" s="11" t="inlineStr">
         <is>
           <t>🟡 平局候选</t>
         </is>
@@ -6306,7 +6306,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="8" t="inlineStr">
+      <c r="A163" s="11" t="inlineStr">
         <is>
           <t>🟡 让球数真实</t>
         </is>
@@ -6725,9 +6725,9 @@
         <is>
           <t xml:space="preserve">时间：22:00
 联赛：英超
-竞彩SP：3.53 / 3.40 / 1.81
-让球SP(真实)：1.75/3.75/3.45
-差值分析：P主=96% P平=100% P客=188%
+竞彩SP：3.40 / 3.40 / 1.85
+让球SP(真实)：1.72/3.80/3.52
+差值分析：P主=100% P平=100% P客=184%
 推荐：客胜 信心7/10 比分1-2(泊松) 半全场胜胜 大小球大2.5(69%) 备选半全场:负胜
 让球:让+1 输盘=让平/让负 </t>
         </is>
@@ -6765,10 +6765,10 @@
         <is>
           <t xml:space="preserve">时间：22:15
 联赛：西甲
-竞彩SP：1.92 / 2.93 / 3.75
-让球SP(真实)：4.26/3.30/1.69
-差值分析：P主=137% P平=90% P客=70%
-推荐：主胜 信心5/10 比分2-1(泊松) 半全场负负 大小球大2.5(70%) 备选半全场:平负
+竞彩SP：1.80 / 2.90 / 4.40
+让球SP(真实)：3.90/3.15/1.80
+差值分析：P主=145% P平=90% P客=59%
+推荐：主胜 信心7/10 比分2-1(泊松) 半全场负负 大小球大2.5(70%) 备选半全场:平负
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6785,9 +6785,9 @@
         <is>
           <t xml:space="preserve">时间：22:30
 联赛：荷乙
-竞彩SP：1.79 / 3.60 / 3.42
-让球SP(真实)：3.45/3.65/1.77
-差值分析：P主=201% P平=100% P客=105%
+竞彩SP：1.76 / 3.60 / 3.53
+让球SP(真实)：3.42/3.55/1.80
+差值分析：P主=205% P平=100% P客=102%
 推荐：主胜 信心7/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(46%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
@@ -6805,9 +6805,9 @@
         <is>
           <t xml:space="preserve">时间：00:00
 联赛：意甲
-竞彩SP：3.70 / 3.40 / 1.77
-让球SP(真实)：1.79/3.55/3.46
-差值分析：P主=87% P平=95% P客=182%
+竞彩SP：3.57 / 3.30 / 1.83
+让球SP(真实)：1.73/3.70/3.56
+差值分析：P主=90% P平=97% P客=175%
 推荐：客胜 信心7/10 比分1-3(泊松) 半全场负负 大小球大2.5(70%) 备选半全场:平负
 让球:让+1 输盘=让平/让负 </t>
         </is>
@@ -6845,9 +6845,9 @@
         <is>
           <t xml:space="preserve">时间：00:30
 联赛：德甲
-竞彩SP：5.00 / 5.00 / 1.37
-让球SP(真实)：2.56/4.10/2.02
-差值分析：P主=78% P平=78% P客=286%
+竞彩SP：4.70 / 4.95 / 1.40
+让球SP(真实)：2.44/4.10/2.10
+差值分析：P主=83% P平=79% P客=280%
 推荐：客胜 信心4/10 比分1-4(泊松) 半全场负负 大小球大2.5(73%) 备选半全场:平负
 让球:让+1 输盘=让平/让负 </t>
         </is>
@@ -6865,9 +6865,9 @@
         <is>
           <t xml:space="preserve">时间：00:30
 联赛：西甲
-竞彩SP：1.90 / 3.35 / 3.28
-让球SP(真实)：3.85/3.60/1.69
-差值分析：P主=176% P平=100% P客=102%
+竞彩SP：1.87 / 3.35 / 3.38
+让球SP(真实)：3.76/3.50/1.73
+差值分析：P主=179% P平=100% P客=99%
 推荐：主胜 信心7/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(71%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
@@ -6885,10 +6885,10 @@
         <is>
           <t xml:space="preserve">时间：01:00
 联赛：美职
-竞彩SP：3.94 / 4.05 / 1.59
-让球SP(真实)：暂无
-差值分析：P主=102% P平=99% P客=253%
-推荐：客胜 信心4/10 比分0-1(泊松) 半全场平负 大小球小2.5(41%) 备选半全场:负负
+竞彩SP：4.18 / 4.15 / 1.54
+让球SP(真实)：2.11/3.65/2.62
+差值分析：P主=97% P平=98% P客=263%
+推荐：客胜 信心4/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
 让球:让0 无让球=— </t>
         </is>
       </c>
@@ -6905,9 +6905,9 @@
         <is>
           <t xml:space="preserve">时间：02:00
 联赛：沙职
-竞彩SP：6.00 / 4.90 / 1.32
-让球SP(真实)：2.77/3.60/2.04
-差值分析：P主=75% P平=92% P客=342%
+竞彩SP：6.50 / 5.15 / 1.28
+让球SP(真实)：2.91/3.70/1.94
+差值分析：P主=70% P平=88% P客=356%
 推荐：客胜 信心9/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
 让球:让0 无让球=— </t>
         </is>
@@ -6925,9 +6925,9 @@
         <is>
           <t xml:space="preserve">时间：02:00
 联赛：法乙
-竞彩SP：2.05 / 3.50 / 2.81
-让球SP(真实)：暂无
-差值分析：P主=151% P平=88% P客=110%
+竞彩SP：2.09 / 3.27 / 2.90
+让球SP(真实)：4.45/3.85/1.55
+差值分析：P主=145% P平=93% P客=105%
 推荐：主胜 信心5/10 比分1-0(泊松) 半全场平胜 大小球小2.5(41%) 备选半全场:胜胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
@@ -6945,9 +6945,9 @@
         <is>
           <t xml:space="preserve">时间：02:45
 联赛：意甲
-竞彩SP：7.00 / 4.16 / 1.34
-让球SP(真实)：2.74/3.25/2.19
-差值分析：P主=48% P平=81% P客=252%
+竞彩SP：6.90 / 4.30 / 1.33
+让球SP(真实)：2.79/3.18/2.19
+差值分析：P主=49% P平=79% P客=255%
 推荐：客胜 信心4/10 比分1-2(泊松) 半全场负负 大小球大2.5(69%) 备选半全场:胜负
 让球:让+1 输盘=让平/让负 </t>
         </is>
@@ -6976,9 +6976,9 @@
   </sheetData>
   <mergeCells count="31">
     <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A51:B51"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A107:B107"/>
-    <mergeCell ref="A51:B51"/>
     <mergeCell ref="A123:B123"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A187:B187"/>
@@ -7097,7 +7097,7 @@
           <t>周六017+周六023</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>·莱红牛:主胜(1.19)
 ·曼城:主胜(1.23)</t>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="G4" s="21" t="inlineStr">
         <is>
-          <t>2.93元</t>
+          <t>2.92元</t>
         </is>
       </c>
       <c r="H4" s="21" t="inlineStr">
@@ -7136,11 +7136,11 @@
           <t>周六017+周六023+周六027</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>·莱红牛:主胜(1.19)
 ·曼城:主胜(1.23)
-·迈季宽广:客胜(1.32)</t>
+·迈季宽广:客胜(1.28)</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
@@ -7176,11 +7176,11 @@
           <t>周六017+周六023+周六027+周六005</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>·莱红牛:主胜(1.19)
 ·曼城:主胜(1.23)
-·迈季宽广:客胜(1.32)
+·迈季宽广:客胜(1.28)
 ·波鸿:客胜(1.70)</t>
         </is>
       </c>
@@ -7197,7 +7197,7 @@
       </c>
       <c r="G6" s="21" t="inlineStr">
         <is>
-          <t>6.57元</t>
+          <t>6.56元</t>
         </is>
       </c>
       <c r="H6" s="21" t="inlineStr">
@@ -7217,11 +7217,11 @@
           <t>周六017+周六023+周六027+周六005+周六006</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>·莱红牛:主胜(1.19)
 ·曼城:主胜(1.23)
-·迈季宽广:客胜(1.32)
+·迈季宽广:客胜(1.28)
 ·波鸿:客胜(1.70)
 ·利物浦:主胜(1.83)</t>
         </is>
@@ -7259,11 +7259,11 @@
           <t>周六017+周六023+周六027+周六005+周六006+周六009</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>·莱红牛:主胜(1.19)
 ·曼城:主胜(1.23)
-·迈季宽广:客胜(1.32)
+·迈季宽广:客胜(1.28)
 ·波鸿:客胜(1.70)
 ·利物浦:主胜(1.83)
 ·萨普斯堡:主胜(1.83)</t>
@@ -7314,7 +7314,7 @@
           <t>周六017+周六023</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>·莱红牛:3-1(6.0)
 ·曼城:4-1(6.2)</t>
@@ -7355,11 +7355,11 @@
           <t>周六017+周六023+周六027</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>·莱红牛:3-1(6.0)
 ·曼城:4-1(6.2)
-·迈季宽广:0-1(6.6)</t>
+·迈季宽广:0-1(6.4)</t>
         </is>
       </c>
       <c r="E11" s="21" t="n">
@@ -7411,11 +7411,11 @@
           <t>周六017+周六023+周六027</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>·莱红牛:主胜(1.19)/让平/让负
 ·曼城:主胜(1.23)/让平/让负
-·迈季宽广:客胜(1.32)/—</t>
+·迈季宽广:客胜(1.28)/—</t>
         </is>
       </c>
       <c r="E13" s="21" t="n">
@@ -7453,11 +7453,11 @@
           <t>周六017+周六023+周六027+周六005</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>·莱红牛:主胜(1.19)/让平/让负
 ·曼城:主胜(1.23)/让平/让负
-·迈季宽广:客胜(1.32)/—
+·迈季宽广:客胜(1.28)/—
 ·波鸿:客胜(1.70)/让平/让负</t>
         </is>
       </c>
@@ -7510,7 +7510,7 @@
           <t>周六017+周六023</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>·莱红牛:胜胜(2.2)
 ·曼城:胜胜(2.2)</t>
@@ -7551,7 +7551,7 @@
           <t>周六017+周六023+周六027</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>·莱红牛:胜胜(2.2)
 ·曼城:胜胜(2.2)
@@ -7593,7 +7593,7 @@
           <t>周六017+周六023+周六027+周六005</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>·莱红牛:胜胜(2.2)
 ·曼城:胜胜(2.2)
@@ -7636,7 +7636,7 @@
           <t>周六017+周六023+周六027+周六005+周六006</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>·莱红牛:胜胜(2.2)
 ·曼城:胜胜(2.2)
@@ -7680,7 +7680,7 @@
           <t>周六017+周六023+周六027+周六005+周六006+周六009</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>·莱红牛:胜胜(2.2)
 ·曼城:胜胜(2.2)

--- a/Aii竞彩推荐_2026-05-09.xlsx
+++ b/Aii竞彩推荐_2026-05-09.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,9 +60,6 @@
       <color rgb="001A3C6E"/>
       <sz val="11"/>
     </font>
-    <font>
-      <sz val="9"/>
-    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -97,7 +94,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -163,17 +160,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -221,9 +212,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -614,7 +602,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：中国竞彩网(sporttery)+500.com · 22:44</t>
+          <t>数据来源：中国竞彩网(sporttery)+500.com · 22:57</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1939,7 @@
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>SP6.50/5.15/1.28 让球0</t>
+          <t>SP6.90/5.25/1.26 让球0</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2087,7 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>📊 竞彩SP数据（含真实让球SP · 22:44）</t>
+          <t>📊 竞彩SP数据（含真实让球SP · 22:57）</t>
         </is>
       </c>
     </row>
@@ -3368,13 +3356,13 @@
         </is>
       </c>
       <c r="D71" s="6" t="n">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="E71" s="6" t="n">
-        <v>5.15</v>
+        <v>5.25</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
@@ -3383,7 +3371,7 @@
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr">
@@ -3393,7 +3381,7 @@
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.89</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4135,7 @@
       </c>
       <c r="G90" s="11" t="inlineStr">
         <is>
-          <t>平平</t>
+          <t>负负</t>
         </is>
       </c>
       <c r="H90" s="11" t="inlineStr">
@@ -4194,7 +4182,7 @@
       </c>
       <c r="F91" s="9" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="G91" s="9" t="inlineStr">
@@ -4303,12 +4291,12 @@
       </c>
       <c r="G93" s="9" t="inlineStr">
         <is>
-          <t>胜胜</t>
+          <t>负负</t>
         </is>
       </c>
       <c r="H93" s="9" t="inlineStr">
         <is>
-          <t>平胜</t>
+          <t>胜负</t>
         </is>
       </c>
       <c r="I93" s="9" t="inlineStr">
@@ -4407,12 +4395,12 @@
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>胜胜</t>
+          <t>负负</t>
         </is>
       </c>
       <c r="H95" s="6" t="inlineStr">
         <is>
-          <t>平胜</t>
+          <t>平负</t>
         </is>
       </c>
       <c r="I95" s="6" t="inlineStr">
@@ -4511,12 +4499,12 @@
       </c>
       <c r="G97" s="9" t="inlineStr">
         <is>
-          <t>负负</t>
+          <t>胜胜</t>
         </is>
       </c>
       <c r="H97" s="9" t="inlineStr">
         <is>
-          <t>平负</t>
+          <t>负胜</t>
         </is>
       </c>
       <c r="I97" s="9" t="inlineStr">
@@ -4615,12 +4603,12 @@
       </c>
       <c r="G99" s="9" t="inlineStr">
         <is>
-          <t>胜胜</t>
+          <t>负负</t>
         </is>
       </c>
       <c r="H99" s="9" t="inlineStr">
         <is>
-          <t>平胜</t>
+          <t>平负</t>
         </is>
       </c>
       <c r="I99" s="9" t="inlineStr">
@@ -4994,7 +4982,7 @@
       </c>
       <c r="J106" s="10" t="inlineStr">
         <is>
-          <t>贝叶斯P主=70%P平=88%P客=356%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球0=无让球/—</t>
+          <t>贝叶斯P主=66%P平=87%P客=362%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5066,7 @@
       </c>
       <c r="F108" s="6" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr">
@@ -5339,7 +5327,7 @@
       </c>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>6.50/5.15/1.28</t>
+          <t>6.90/5.25/1.26</t>
         </is>
       </c>
       <c r="G117" s="6" t="inlineStr">
@@ -6071,7 +6059,7 @@
         <is>
           <t>·莱红牛:主胜(1.19)
 ·曼城:主胜(1.23)
-·迈季宽广:客胜(1.28)</t>
+·迈季宽广:客胜(1.26)</t>
         </is>
       </c>
       <c r="D151" s="6" t="n">
@@ -6084,12 +6072,12 @@
       </c>
       <c r="F151" s="6" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="G151" s="6" t="inlineStr">
         <is>
-          <t>1.19×1.23×1.28=1.87</t>
+          <t>1.19×1.23×1.26=1.84</t>
         </is>
       </c>
     </row>
@@ -6108,7 +6096,7 @@
         <is>
           <t>·莱红牛:主胜(1.19)
 ·曼城:主胜(1.23)
-·迈季宽广:客胜(1.28)
+·迈季宽广:客胜(1.26)
 ·波鸿:客胜(1.70)</t>
         </is>
       </c>
@@ -6122,12 +6110,12 @@
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="G152" s="6" t="inlineStr">
         <is>
-          <t>1.19×1.23×1.28×1.70=3.19</t>
+          <t>1.19×1.23×1.26×1.70=3.14</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6134,7 @@
         <is>
           <t>·莱红牛:主胜(1.19)
 ·曼城:主胜(1.23)
-·迈季宽广:客胜(1.28)
+·迈季宽广:客胜(1.26)
 ·波鸿:客胜(1.70)
 ·利物浦:主胜(1.83)</t>
         </is>
@@ -6161,12 +6149,12 @@
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="G153" s="6" t="inlineStr">
         <is>
-          <t>1.19×1.23×1.28×1.70×1.83=5.83</t>
+          <t>1.19×1.23×1.26×1.70×1.83=5.74</t>
         </is>
       </c>
     </row>
@@ -6185,7 +6173,7 @@
         <is>
           <t>·莱红牛:主胜(1.19)
 ·曼城:主胜(1.23)
-·迈季宽广:客胜(1.28)
+·迈季宽广:客胜(1.26)
 ·波鸿:客胜(1.70)
 ·利物浦:主胜(1.83)
 ·萨普斯堡:主胜(1.83)</t>
@@ -6201,12 +6189,12 @@
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>10.50</t>
         </is>
       </c>
       <c r="G154" s="6" t="inlineStr">
         <is>
-          <t>1.19×1.23×1.28×1.70×1.83×1.83=10.67</t>
+          <t>1.19×1.23×1.26×1.70×1.83×1.83=10.50</t>
         </is>
       </c>
     </row>
@@ -6905,9 +6893,9 @@
         <is>
           <t xml:space="preserve">时间：02:00
 联赛：沙职
-竞彩SP：6.50 / 5.15 / 1.28
-让球SP(真实)：2.91/3.70/1.94
-差值分析：P主=70% P平=88% P客=356%
+竞彩SP：6.90 / 5.25 / 1.26
+让球SP(真实)：3.03/3.70/1.89
+差值分析：P主=66% P平=87% P客=362%
 推荐：客胜 信心9/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
 让球:让0 无让球=— </t>
         </is>
@@ -6976,8 +6964,8 @@
   </sheetData>
   <mergeCells count="31">
     <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A11:B11"/>
     <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A11:B11"/>
     <mergeCell ref="A107:B107"/>
     <mergeCell ref="A123:B123"/>
     <mergeCell ref="A1:B1"/>
@@ -7106,22 +7094,19 @@
       <c r="D4" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="21" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="F4" s="21" t="inlineStr">
-        <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="G4" s="21" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>2注×2元</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>2.92元</t>
         </is>
       </c>
-      <c r="H4" s="21" t="inlineStr">
-        <is>
-          <t>+46%</t>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>1.46倍</t>
         </is>
       </c>
     </row>
@@ -7140,28 +7125,25 @@
         <is>
           <t>·莱红牛:主胜(1.19)
 ·曼城:主胜(1.23)
-·迈季宽广:客胜(1.28)</t>
+·迈季宽广:客胜(1.26)</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="21" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="F5" s="21" t="inlineStr">
-        <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="G5" s="21" t="inlineStr">
-        <is>
-          <t>3.86元</t>
-        </is>
-      </c>
-      <c r="H5" s="21" t="inlineStr">
-        <is>
-          <t>+93%</t>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>2注×2元</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>3.68元</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>1.84倍</t>
         </is>
       </c>
     </row>
@@ -7180,29 +7162,26 @@
         <is>
           <t>·莱红牛:主胜(1.19)
 ·曼城:主胜(1.23)
-·迈季宽广:客胜(1.28)
+·迈季宽广:客胜(1.26)
 ·波鸿:客胜(1.70)</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="21" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="G6" s="21" t="inlineStr">
-        <is>
-          <t>6.56元</t>
-        </is>
-      </c>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t>+228%</t>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>2注×2元</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>6.28元</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>3.14倍</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7200,7 @@
         <is>
           <t>·莱红牛:主胜(1.19)
 ·曼城:主胜(1.23)
-·迈季宽广:客胜(1.28)
+·迈季宽广:客胜(1.26)
 ·波鸿:客胜(1.70)
 ·利物浦:主胜(1.83)</t>
         </is>
@@ -7229,22 +7208,19 @@
       <c r="D7" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="21" t="n">
-        <v>6.01</v>
-      </c>
-      <c r="F7" s="21" t="inlineStr">
-        <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="G7" s="21" t="inlineStr">
-        <is>
-          <t>12.02元</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t>+501%</t>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>2注×2元</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>11.48元</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>5.74倍</t>
         </is>
       </c>
     </row>
@@ -7263,7 +7239,7 @@
         <is>
           <t>·莱红牛:主胜(1.19)
 ·曼城:主胜(1.23)
-·迈季宽广:客胜(1.28)
+·迈季宽广:客胜(1.26)
 ·波鸿:客胜(1.70)
 ·利物浦:主胜(1.83)
 ·萨普斯堡:主胜(1.83)</t>
@@ -7272,22 +7248,19 @@
       <c r="D8" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="21" t="n">
-        <v>11</v>
-      </c>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="G8" s="21" t="inlineStr">
-        <is>
-          <t>22.00元</t>
-        </is>
-      </c>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t>+1000%</t>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>2注×2元</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>21.00元</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>10.50倍</t>
         </is>
       </c>
     </row>
@@ -7320,22 +7293,22 @@
 ·曼城:4-1(6.2)</t>
         </is>
       </c>
-      <c r="E10" s="21" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="F10" s="21" t="inlineStr">
+      <c r="E10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
-        <is>
-          <t>74.40元</t>
-        </is>
-      </c>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t>+3620%</t>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>约74元</t>
         </is>
       </c>
     </row>
@@ -7359,25 +7332,25 @@
         <is>
           <t>·莱红牛:3-1(6.0)
 ·曼城:4-1(6.2)
-·迈季宽广:0-1(6.4)</t>
-        </is>
-      </c>
-      <c r="E11" s="21" t="n">
-        <v>245.5</v>
-      </c>
-      <c r="F11" s="21" t="inlineStr">
+·迈季宽广:0-1(6.3)</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="G11" s="21" t="inlineStr">
-        <is>
-          <t>491.00元</t>
-        </is>
-      </c>
-      <c r="H11" s="21" t="inlineStr">
-        <is>
-          <t>+24450%</t>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>约465元</t>
         </is>
       </c>
     </row>
@@ -7415,25 +7388,25 @@
         <is>
           <t>·莱红牛:主胜(1.19)/让平/让负
 ·曼城:主胜(1.23)/让平/让负
-·迈季宽广:客胜(1.28)/—</t>
-        </is>
-      </c>
-      <c r="E13" s="21" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="F13" s="21" t="inlineStr">
+·迈季宽广:客胜(1.26)/—</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="G13" s="21" t="inlineStr">
-        <is>
-          <t>3.86元</t>
-        </is>
-      </c>
-      <c r="H13" s="21" t="inlineStr">
-        <is>
-          <t>+93%</t>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>3.69元</t>
         </is>
       </c>
     </row>
@@ -7457,26 +7430,26 @@
         <is>
           <t>·莱红牛:主胜(1.19)/让平/让负
 ·曼城:主胜(1.23)/让平/让负
-·迈季宽广:客胜(1.28)/—
+·迈季宽广:客胜(1.26)/—
 ·波鸿:客胜(1.70)/让平/让负</t>
         </is>
       </c>
-      <c r="E14" s="21" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="F14" s="21" t="inlineStr">
+      <c r="E14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="G14" s="21" t="inlineStr">
-        <is>
-          <t>6.56元</t>
-        </is>
-      </c>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t>+228%</t>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>6.27元</t>
         </is>
       </c>
     </row>
@@ -7516,22 +7489,22 @@
 ·曼城:胜胜(2.2)</t>
         </is>
       </c>
-      <c r="E16" s="21" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="F16" s="21" t="inlineStr">
+      <c r="E16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>4.84</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="G16" s="21" t="inlineStr">
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>9.68元</t>
-        </is>
-      </c>
-      <c r="H16" s="21" t="inlineStr">
-        <is>
-          <t>+384%</t>
         </is>
       </c>
     </row>
@@ -7558,22 +7531,22 @@
 ·迈季宽广:负负(2.5)</t>
         </is>
       </c>
-      <c r="E17" s="21" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="F17" s="21" t="inlineStr">
+      <c r="E17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>12.10</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="G17" s="21" t="inlineStr">
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>24.20元</t>
-        </is>
-      </c>
-      <c r="H17" s="21" t="inlineStr">
-        <is>
-          <t>+1110%</t>
         </is>
       </c>
     </row>
@@ -7601,22 +7574,22 @@
 ·波鸿:负负(2.5)</t>
         </is>
       </c>
-      <c r="E18" s="21" t="n">
-        <v>30.25</v>
-      </c>
-      <c r="F18" s="21" t="inlineStr">
+      <c r="E18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>30.25</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="G18" s="21" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>60.50元</t>
-        </is>
-      </c>
-      <c r="H18" s="21" t="inlineStr">
-        <is>
-          <t>+2925%</t>
         </is>
       </c>
     </row>
@@ -7645,22 +7618,22 @@
 ·利物浦:胜胜(2.2)</t>
         </is>
       </c>
-      <c r="E19" s="21" t="n">
-        <v>66.55</v>
-      </c>
-      <c r="F19" s="21" t="inlineStr">
+      <c r="E19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>66.55</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="G19" s="21" t="inlineStr">
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>133.10元</t>
-        </is>
-      </c>
-      <c r="H19" s="21" t="inlineStr">
-        <is>
-          <t>+6555%</t>
         </is>
       </c>
     </row>
@@ -7690,22 +7663,22 @@
 ·萨普斯堡:胜胜(2.2)</t>
         </is>
       </c>
-      <c r="E20" s="21" t="n">
-        <v>146.41</v>
-      </c>
-      <c r="F20" s="21" t="inlineStr">
+      <c r="E20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>146.41</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="G20" s="21" t="inlineStr">
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>292.82元</t>
-        </is>
-      </c>
-      <c r="H20" s="21" t="inlineStr">
-        <is>
-          <t>+14541%</t>
         </is>
       </c>
     </row>

--- a/Aii竞彩推荐_2026-05-09.xlsx
+++ b/Aii竞彩推荐_2026-05-09.xlsx
@@ -602,7 +602,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：中国竞彩网(sporttery)+500.com · 22:57</t>
+          <t>数据来源：中国竞彩网(sporttery)+500.com · 23:42</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>📊 竞彩SP数据（含真实让球SP · 22:57）</t>
+          <t>📊 竞彩SP数据（含真实让球SP · 23:42）</t>
         </is>
       </c>
     </row>

--- a/Aii竞彩推荐_2026-05-09.xlsx
+++ b/Aii竞彩推荐_2026-05-09.xlsx
@@ -602,7 +602,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：中国竞彩网(sporttery)+500.com · 23:42</t>
+          <t>数据来源：中国竞彩网(sporttery)+500.com · 23:49</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>📊 竞彩SP数据（含真实让球SP · 23:42）</t>
+          <t>📊 竞彩SP数据（含真实让球SP · 23:49）</t>
         </is>
       </c>
     </row>

--- a/Aii竞彩推荐_2026-05-09.xlsx
+++ b/Aii竞彩推荐_2026-05-09.xlsx
@@ -80,12 +80,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C8E6C9"/>
+        <fgColor rgb="00FFF9C4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF9C4"/>
+        <fgColor rgb="00C8E6C9"/>
       </patternFill>
     </fill>
     <fill>
@@ -201,7 +201,7 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -602,7 +602,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：中国竞彩网(sporttery)+500.com · 23:49</t>
+          <t>数据来源：中国竞彩网(sporttery)+500.com · 23:56</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>📊 竞彩SP数据（含真实让球SP · 23:49）</t>
+          <t>📊 竞彩SP数据（含真实让球SP · 23:56）</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>5/10</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>5/10</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
@@ -3791,104 +3791,104 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="9" t="inlineStr">
+      <c r="A84" s="6" t="inlineStr">
         <is>
           <t>周六005</t>
         </is>
       </c>
-      <c r="B84" s="9" t="inlineStr">
+      <c r="B84" s="6" t="inlineStr">
         <is>
           <t>波鸿vs汉诺威96</t>
         </is>
       </c>
-      <c r="C84" s="9" t="inlineStr">
+      <c r="C84" s="6" t="inlineStr">
         <is>
           <t>客胜</t>
         </is>
       </c>
-      <c r="D84" s="9" t="inlineStr">
-        <is>
-          <t>7/10</t>
-        </is>
-      </c>
-      <c r="E84" s="9" t="inlineStr">
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>6/10</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
         <is>
           <t>1-2</t>
         </is>
       </c>
-      <c r="F84" s="9" t="inlineStr">
+      <c r="F84" s="6" t="inlineStr">
         <is>
           <t>1-3</t>
         </is>
       </c>
-      <c r="G84" s="9" t="inlineStr">
+      <c r="G84" s="6" t="inlineStr">
         <is>
           <t>负负</t>
         </is>
       </c>
-      <c r="H84" s="9" t="inlineStr">
+      <c r="H84" s="6" t="inlineStr">
         <is>
           <t>平负</t>
         </is>
       </c>
-      <c r="I84" s="9" t="inlineStr">
+      <c r="I84" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="J84" s="10" t="inlineStr">
+      <c r="J84" s="8" t="inlineStr">
         <is>
           <t>贝叶斯P主=98%P平=96%P客=211%|泊松比分1-2|半全场负负|大小球大2.5(70%)|让球+1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="9" t="inlineStr">
+      <c r="A85" s="6" t="inlineStr">
         <is>
           <t>周六006</t>
         </is>
       </c>
-      <c r="B85" s="9" t="inlineStr">
+      <c r="B85" s="6" t="inlineStr">
         <is>
           <t>利物浦vs切尔西</t>
         </is>
       </c>
-      <c r="C85" s="9" t="inlineStr">
+      <c r="C85" s="6" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="D85" s="9" t="inlineStr">
-        <is>
-          <t>7/10</t>
-        </is>
-      </c>
-      <c r="E85" s="9" t="inlineStr">
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>6/10</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="F85" s="9" t="inlineStr">
+      <c r="F85" s="6" t="inlineStr">
         <is>
           <t>3-1</t>
         </is>
       </c>
-      <c r="G85" s="9" t="inlineStr">
+      <c r="G85" s="6" t="inlineStr">
         <is>
           <t>胜胜</t>
         </is>
       </c>
-      <c r="H85" s="9" t="inlineStr">
+      <c r="H85" s="6" t="inlineStr">
         <is>
           <t>平胜</t>
         </is>
       </c>
-      <c r="I85" s="9" t="inlineStr">
+      <c r="I85" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="J85" s="10" t="inlineStr">
+      <c r="J85" s="8" t="inlineStr">
         <is>
           <t>贝叶斯P主=199%P平=100%P客=113%|泊松比分2-1|半全场胜胜|大小球大2.5(70%)|让球-1=输盘/让平/让负</t>
         </is>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
@@ -3999,52 +3999,52 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="9" t="inlineStr">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>周六009</t>
         </is>
       </c>
-      <c r="B88" s="9" t="inlineStr">
+      <c r="B88" s="6" t="inlineStr">
         <is>
           <t>萨普斯堡vs腓特烈</t>
         </is>
       </c>
-      <c r="C88" s="9" t="inlineStr">
+      <c r="C88" s="6" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="D88" s="9" t="inlineStr">
-        <is>
-          <t>7/10</t>
-        </is>
-      </c>
-      <c r="E88" s="9" t="inlineStr">
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>6/10</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
         <is>
           <t>1-0</t>
         </is>
       </c>
-      <c r="F88" s="9" t="inlineStr">
+      <c r="F88" s="6" t="inlineStr">
         <is>
           <t>2-0</t>
         </is>
       </c>
-      <c r="G88" s="9" t="inlineStr">
+      <c r="G88" s="6" t="inlineStr">
         <is>
           <t>胜胜</t>
         </is>
       </c>
-      <c r="H88" s="9" t="inlineStr">
+      <c r="H88" s="6" t="inlineStr">
         <is>
           <t>平胜</t>
         </is>
       </c>
-      <c r="I88" s="9" t="inlineStr">
+      <c r="I88" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="J88" s="10" t="inlineStr">
+      <c r="J88" s="8" t="inlineStr">
         <is>
           <t>贝叶斯P主=199%P平=100%P客=113%|泊松比分1-0|半全场胜胜|大小球小2.5(44%)|让球-1=输盘/让平/让负</t>
         </is>
@@ -4068,139 +4068,139 @@
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
+          <t>5/10</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>平胜</t>
+        </is>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>2元</t>
+        </is>
+      </c>
+      <c r="J89" s="8" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=265%P平=89%P客=59%|泊松比分2-0|半全场胜胜|大小球小2.5(43%)|让球-1=输盘/让平/让负</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="9" t="inlineStr">
+        <is>
+          <t>周六011</t>
+        </is>
+      </c>
+      <c r="B90" s="9" t="inlineStr">
+        <is>
+          <t>卡利亚里vs乌迪内斯</t>
+        </is>
+      </c>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>平局</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="inlineStr">
+        <is>
           <t>4/10</t>
         </is>
       </c>
-      <c r="E89" s="6" t="inlineStr">
-        <is>
-          <t>2-0</t>
-        </is>
-      </c>
-      <c r="F89" s="6" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="G89" s="6" t="inlineStr">
-        <is>
-          <t>胜胜</t>
-        </is>
-      </c>
-      <c r="H89" s="6" t="inlineStr">
-        <is>
-          <t>平胜</t>
-        </is>
-      </c>
-      <c r="I89" s="6" t="inlineStr">
+      <c r="E90" s="9" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="F90" s="9" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="G90" s="9" t="inlineStr">
+        <is>
+          <t>负负</t>
+        </is>
+      </c>
+      <c r="H90" s="9" t="inlineStr">
+        <is>
+          <t>平负</t>
+        </is>
+      </c>
+      <c r="I90" s="9" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="J89" s="8" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=265%P平=89%P客=59%|泊松比分2-0|半全场胜胜|大小球小2.5(43%)|让球-1=输盘/让平/让负</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="11" t="inlineStr">
-        <is>
-          <t>周六011</t>
-        </is>
-      </c>
-      <c r="B90" s="11" t="inlineStr">
-        <is>
-          <t>卡利亚里vs乌迪内斯</t>
-        </is>
-      </c>
-      <c r="C90" s="11" t="inlineStr">
-        <is>
-          <t>平局</t>
-        </is>
-      </c>
-      <c r="D90" s="11" t="inlineStr">
-        <is>
-          <t>5/10</t>
-        </is>
-      </c>
-      <c r="E90" s="11" t="inlineStr">
-        <is>
-          <t>2-2</t>
-        </is>
-      </c>
-      <c r="F90" s="11" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
-      </c>
-      <c r="G90" s="11" t="inlineStr">
+      <c r="J90" s="10" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=88%P平=79%P客=74%|泊松比分2-2|半全场负负|大小球大2.5(69%)|让球-1=输盘/让平/让负|平SP低+联赛特征</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>周六012</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>代格福什vs米亚尔比</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>6/10</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>平负</t>
+        </is>
+      </c>
+      <c r="H91" s="6" t="inlineStr">
         <is>
           <t>负负</t>
         </is>
       </c>
-      <c r="H90" s="11" t="inlineStr">
-        <is>
-          <t>平负</t>
-        </is>
-      </c>
-      <c r="I90" s="11" t="inlineStr">
+      <c r="I91" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="J90" s="12" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=88%P平=79%P客=74%|泊松比分2-2|半全场负负|大小球大2.5(69%)|让球-1=输盘/让平/让负|平SP低+联赛特征</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="9" t="inlineStr">
-        <is>
-          <t>周六012</t>
-        </is>
-      </c>
-      <c r="B91" s="9" t="inlineStr">
-        <is>
-          <t>代格福什vs米亚尔比</t>
-        </is>
-      </c>
-      <c r="C91" s="9" t="inlineStr">
-        <is>
-          <t>客胜</t>
-        </is>
-      </c>
-      <c r="D91" s="9" t="inlineStr">
-        <is>
-          <t>7/10</t>
-        </is>
-      </c>
-      <c r="E91" s="9" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="F91" s="9" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="G91" s="9" t="inlineStr">
-        <is>
-          <t>平负</t>
-        </is>
-      </c>
-      <c r="H91" s="9" t="inlineStr">
-        <is>
-          <t>负负</t>
-        </is>
-      </c>
-      <c r="I91" s="9" t="inlineStr">
-        <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="J91" s="10" t="inlineStr">
+      <c r="J91" s="8" t="inlineStr">
         <is>
           <t>贝叶斯P主=91%P平=100%P客=168%|泊松比分0-1|半全场平负|大小球小2.5(42%)|让球+1=输盘/让平/让负</t>
         </is>
@@ -4224,7 +4224,7 @@
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>5/10</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -4259,52 +4259,52 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="9" t="inlineStr">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t>周六014</t>
         </is>
       </c>
-      <c r="B93" s="9" t="inlineStr">
+      <c r="B93" s="6" t="inlineStr">
         <is>
           <t>奥格斯堡vs门兴</t>
         </is>
       </c>
-      <c r="C93" s="9" t="inlineStr">
+      <c r="C93" s="6" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="D93" s="9" t="inlineStr">
-        <is>
-          <t>7/10</t>
-        </is>
-      </c>
-      <c r="E93" s="9" t="inlineStr">
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>6/10</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
         <is>
           <t>3-2</t>
         </is>
       </c>
-      <c r="F93" s="9" t="inlineStr">
+      <c r="F93" s="6" t="inlineStr">
         <is>
           <t>2-3</t>
         </is>
       </c>
-      <c r="G93" s="9" t="inlineStr">
+      <c r="G93" s="6" t="inlineStr">
         <is>
           <t>负负</t>
         </is>
       </c>
-      <c r="H93" s="9" t="inlineStr">
+      <c r="H93" s="6" t="inlineStr">
         <is>
           <t>胜负</t>
         </is>
       </c>
-      <c r="I93" s="9" t="inlineStr">
+      <c r="I93" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="J93" s="10" t="inlineStr">
+      <c r="J93" s="8" t="inlineStr">
         <is>
           <t>贝叶斯P主=211%P平=98%P客=111%|泊松比分3-2|半全场负负|大小球大2.5(72%)|让球-1=输盘/让平/让负</t>
         </is>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>5/10</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
@@ -4415,104 +4415,104 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="9" t="inlineStr">
+      <c r="A96" s="11" t="inlineStr">
         <is>
           <t>周六017</t>
         </is>
       </c>
-      <c r="B96" s="9" t="inlineStr">
+      <c r="B96" s="11" t="inlineStr">
         <is>
           <t>莱红牛vs圣保利</t>
         </is>
       </c>
-      <c r="C96" s="9" t="inlineStr">
+      <c r="C96" s="11" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="D96" s="9" t="inlineStr">
+      <c r="D96" s="11" t="inlineStr">
         <is>
           <t>9/10</t>
         </is>
       </c>
-      <c r="E96" s="9" t="inlineStr">
+      <c r="E96" s="11" t="inlineStr">
         <is>
           <t>3-1</t>
         </is>
       </c>
-      <c r="F96" s="9" t="inlineStr">
+      <c r="F96" s="11" t="inlineStr">
         <is>
           <t>3-2</t>
         </is>
       </c>
-      <c r="G96" s="9" t="inlineStr">
+      <c r="G96" s="11" t="inlineStr">
         <is>
           <t>胜胜</t>
         </is>
       </c>
-      <c r="H96" s="9" t="inlineStr">
+      <c r="H96" s="11" t="inlineStr">
         <is>
           <t>平胜</t>
         </is>
       </c>
-      <c r="I96" s="9" t="inlineStr">
+      <c r="I96" s="11" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="J96" s="10" t="inlineStr">
+      <c r="J96" s="12" t="inlineStr">
         <is>
           <t>贝叶斯P主=336%P平=71%P客=44%|泊松比分3-1|半全场胜胜|大小球大2.5(71%)|让球-2=输盘/让平/让负⚠️让-2深盘·主胜可能不穿盘</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="9" t="inlineStr">
+      <c r="A97" s="6" t="inlineStr">
         <is>
           <t>周六018</t>
         </is>
       </c>
-      <c r="B97" s="9" t="inlineStr">
+      <c r="B97" s="6" t="inlineStr">
         <is>
           <t>桑德兰vs曼联</t>
         </is>
       </c>
-      <c r="C97" s="9" t="inlineStr">
+      <c r="C97" s="6" t="inlineStr">
         <is>
           <t>客胜</t>
         </is>
       </c>
-      <c r="D97" s="9" t="inlineStr">
-        <is>
-          <t>7/10</t>
-        </is>
-      </c>
-      <c r="E97" s="9" t="inlineStr">
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>6/10</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
         <is>
           <t>1-2</t>
         </is>
       </c>
-      <c r="F97" s="9" t="inlineStr">
+      <c r="F97" s="6" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="G97" s="9" t="inlineStr">
+      <c r="G97" s="6" t="inlineStr">
         <is>
           <t>胜胜</t>
         </is>
       </c>
-      <c r="H97" s="9" t="inlineStr">
+      <c r="H97" s="6" t="inlineStr">
         <is>
           <t>负胜</t>
         </is>
       </c>
-      <c r="I97" s="9" t="inlineStr">
+      <c r="I97" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="J97" s="10" t="inlineStr">
+      <c r="J97" s="8" t="inlineStr">
         <is>
           <t>贝叶斯P主=100%P平=100%P客=184%|泊松比分1-2|半全场胜胜|大小球大2.5(69%)|让球+1=输盘/让平/让负</t>
         </is>
@@ -4536,7 +4536,7 @@
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -4571,208 +4571,208 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="9" t="inlineStr">
+      <c r="A99" s="6" t="inlineStr">
         <is>
           <t>周六020</t>
         </is>
       </c>
-      <c r="B99" s="9" t="inlineStr">
+      <c r="B99" s="6" t="inlineStr">
         <is>
           <t>塞维利亚vs西班牙人</t>
         </is>
       </c>
-      <c r="C99" s="9" t="inlineStr">
+      <c r="C99" s="6" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="D99" s="9" t="inlineStr">
-        <is>
-          <t>7/10</t>
-        </is>
-      </c>
-      <c r="E99" s="9" t="inlineStr">
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>6/10</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="F99" s="9" t="inlineStr">
+      <c r="F99" s="6" t="inlineStr">
         <is>
           <t>1-2</t>
         </is>
       </c>
-      <c r="G99" s="9" t="inlineStr">
+      <c r="G99" s="6" t="inlineStr">
         <is>
           <t>负负</t>
         </is>
       </c>
-      <c r="H99" s="9" t="inlineStr">
+      <c r="H99" s="6" t="inlineStr">
         <is>
           <t>平负</t>
         </is>
       </c>
-      <c r="I99" s="9" t="inlineStr">
+      <c r="I99" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="J99" s="10" t="inlineStr">
+      <c r="J99" s="8" t="inlineStr">
         <is>
           <t>贝叶斯P主=145%P平=90%P客=59%|泊松比分2-1|半全场负负|大小球大2.5(70%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="9" t="inlineStr">
+      <c r="A100" s="6" t="inlineStr">
         <is>
           <t>周六021</t>
         </is>
       </c>
-      <c r="B100" s="9" t="inlineStr">
+      <c r="B100" s="6" t="inlineStr">
         <is>
           <t>威廉二世vs瓦尔韦克</t>
         </is>
       </c>
-      <c r="C100" s="9" t="inlineStr">
+      <c r="C100" s="6" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="D100" s="9" t="inlineStr">
-        <is>
-          <t>7/10</t>
-        </is>
-      </c>
-      <c r="E100" s="9" t="inlineStr">
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>6/10</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
         <is>
           <t>2-0</t>
         </is>
       </c>
-      <c r="F100" s="9" t="inlineStr">
+      <c r="F100" s="6" t="inlineStr">
         <is>
           <t>1-0</t>
         </is>
       </c>
-      <c r="G100" s="9" t="inlineStr">
+      <c r="G100" s="6" t="inlineStr">
         <is>
           <t>胜胜</t>
         </is>
       </c>
-      <c r="H100" s="9" t="inlineStr">
+      <c r="H100" s="6" t="inlineStr">
         <is>
           <t>平胜</t>
         </is>
       </c>
-      <c r="I100" s="9" t="inlineStr">
+      <c r="I100" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="J100" s="10" t="inlineStr">
+      <c r="J100" s="8" t="inlineStr">
         <is>
           <t>贝叶斯P主=205%P平=100%P客=102%|泊松比分2-0|半全场胜胜|大小球小2.5(46%)|让球-1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="9" t="inlineStr">
+      <c r="A101" s="6" t="inlineStr">
         <is>
           <t>周六022</t>
         </is>
       </c>
-      <c r="B101" s="9" t="inlineStr">
+      <c r="B101" s="6" t="inlineStr">
         <is>
           <t>拉齐奥vs国际米兰</t>
         </is>
       </c>
-      <c r="C101" s="9" t="inlineStr">
+      <c r="C101" s="6" t="inlineStr">
         <is>
           <t>客胜</t>
         </is>
       </c>
-      <c r="D101" s="9" t="inlineStr">
-        <is>
-          <t>7/10</t>
-        </is>
-      </c>
-      <c r="E101" s="9" t="inlineStr">
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>6/10</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
         <is>
           <t>1-3</t>
         </is>
       </c>
-      <c r="F101" s="9" t="inlineStr">
+      <c r="F101" s="6" t="inlineStr">
         <is>
           <t>1-2</t>
         </is>
       </c>
-      <c r="G101" s="9" t="inlineStr">
+      <c r="G101" s="6" t="inlineStr">
         <is>
           <t>负负</t>
         </is>
       </c>
-      <c r="H101" s="9" t="inlineStr">
+      <c r="H101" s="6" t="inlineStr">
         <is>
           <t>平负</t>
         </is>
       </c>
-      <c r="I101" s="9" t="inlineStr">
+      <c r="I101" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="J101" s="10" t="inlineStr">
+      <c r="J101" s="8" t="inlineStr">
         <is>
           <t>贝叶斯P主=90%P平=97%P客=175%|泊松比分1-3|半全场负负|大小球大2.5(70%)|让球+1=输盘/让平/让负</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="9" t="inlineStr">
+      <c r="A102" s="11" t="inlineStr">
         <is>
           <t>周六023</t>
         </is>
       </c>
-      <c r="B102" s="9" t="inlineStr">
+      <c r="B102" s="11" t="inlineStr">
         <is>
           <t>曼城vs布伦特</t>
         </is>
       </c>
-      <c r="C102" s="9" t="inlineStr">
+      <c r="C102" s="11" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="D102" s="9" t="inlineStr">
+      <c r="D102" s="11" t="inlineStr">
         <is>
           <t>9/10</t>
         </is>
       </c>
-      <c r="E102" s="9" t="inlineStr">
+      <c r="E102" s="11" t="inlineStr">
         <is>
           <t>4-1</t>
         </is>
       </c>
-      <c r="F102" s="9" t="inlineStr">
+      <c r="F102" s="11" t="inlineStr">
         <is>
           <t>3-1</t>
         </is>
       </c>
-      <c r="G102" s="9" t="inlineStr">
+      <c r="G102" s="11" t="inlineStr">
         <is>
           <t>胜胜</t>
         </is>
       </c>
-      <c r="H102" s="9" t="inlineStr">
+      <c r="H102" s="11" t="inlineStr">
         <is>
           <t>平胜</t>
         </is>
       </c>
-      <c r="I102" s="9" t="inlineStr">
+      <c r="I102" s="11" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="J102" s="10" t="inlineStr">
+      <c r="J102" s="12" t="inlineStr">
         <is>
           <t>贝叶斯P主=324%P平=72%P客=53%|泊松比分4-1|半全场胜胜|大小球大2.5(72%)|让球-1=输盘/让平/让负</t>
         </is>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>5/10</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
@@ -4831,52 +4831,52 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="9" t="inlineStr">
+      <c r="A104" s="6" t="inlineStr">
         <is>
           <t>周六025</t>
         </is>
       </c>
-      <c r="B104" s="9" t="inlineStr">
+      <c r="B104" s="6" t="inlineStr">
         <is>
           <t>马竞vs塞尔塔</t>
         </is>
       </c>
-      <c r="C104" s="9" t="inlineStr">
+      <c r="C104" s="6" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="D104" s="9" t="inlineStr">
-        <is>
-          <t>7/10</t>
-        </is>
-      </c>
-      <c r="E104" s="9" t="inlineStr">
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>6/10</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
         <is>
           <t>3-1</t>
         </is>
       </c>
-      <c r="F104" s="9" t="inlineStr">
+      <c r="F104" s="6" t="inlineStr">
         <is>
           <t>4-1</t>
         </is>
       </c>
-      <c r="G104" s="9" t="inlineStr">
+      <c r="G104" s="6" t="inlineStr">
         <is>
           <t>胜胜</t>
         </is>
       </c>
-      <c r="H104" s="9" t="inlineStr">
+      <c r="H104" s="6" t="inlineStr">
         <is>
           <t>平胜</t>
         </is>
       </c>
-      <c r="I104" s="9" t="inlineStr">
+      <c r="I104" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="J104" s="10" t="inlineStr">
+      <c r="J104" s="8" t="inlineStr">
         <is>
           <t>贝叶斯P主=179%P平=100%P客=99%|泊松比分3-1|半全场胜胜|大小球大2.5(71%)|让球-1=输盘/让平/让负</t>
         </is>
@@ -4900,7 +4900,7 @@
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>5/10</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
@@ -4935,52 +4935,52 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="9" t="inlineStr">
+      <c r="A106" s="11" t="inlineStr">
         <is>
           <t>周六027</t>
         </is>
       </c>
-      <c r="B106" s="9" t="inlineStr">
+      <c r="B106" s="11" t="inlineStr">
         <is>
           <t>迈季宽广vs胡巴卡德</t>
         </is>
       </c>
-      <c r="C106" s="9" t="inlineStr">
+      <c r="C106" s="11" t="inlineStr">
         <is>
           <t>客胜</t>
         </is>
       </c>
-      <c r="D106" s="9" t="inlineStr">
+      <c r="D106" s="11" t="inlineStr">
         <is>
           <t>9/10</t>
         </is>
       </c>
-      <c r="E106" s="9" t="inlineStr">
+      <c r="E106" s="11" t="inlineStr">
         <is>
           <t>0-1</t>
         </is>
       </c>
-      <c r="F106" s="9" t="inlineStr">
+      <c r="F106" s="11" t="inlineStr">
         <is>
           <t>0-2</t>
         </is>
       </c>
-      <c r="G106" s="9" t="inlineStr">
+      <c r="G106" s="11" t="inlineStr">
         <is>
           <t>负负</t>
         </is>
       </c>
-      <c r="H106" s="9" t="inlineStr">
+      <c r="H106" s="11" t="inlineStr">
         <is>
           <t>平负</t>
         </is>
       </c>
-      <c r="I106" s="9" t="inlineStr">
+      <c r="I106" s="11" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="J106" s="10" t="inlineStr">
+      <c r="J106" s="12" t="inlineStr">
         <is>
           <t>贝叶斯P主=66%P平=87%P客=362%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球0=无让球/—</t>
         </is>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>4/10</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>5/10</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -5202,100 +5202,100 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="9" t="n">
+      <c r="A115" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="B115" s="9" t="inlineStr">
+      <c r="B115" s="11" t="inlineStr">
         <is>
           <t>周六017</t>
         </is>
       </c>
-      <c r="C115" s="9" t="inlineStr">
+      <c r="C115" s="11" t="inlineStr">
         <is>
           <t>德甲</t>
         </is>
       </c>
-      <c r="D115" s="9" t="inlineStr">
+      <c r="D115" s="11" t="inlineStr">
         <is>
           <t>莱红牛</t>
         </is>
       </c>
-      <c r="E115" s="9" t="inlineStr">
+      <c r="E115" s="11" t="inlineStr">
         <is>
           <t>圣保利</t>
         </is>
       </c>
-      <c r="F115" s="9" t="inlineStr">
+      <c r="F115" s="11" t="inlineStr">
         <is>
           <t>1.19/5.65/9.00</t>
         </is>
       </c>
-      <c r="G115" s="9" t="inlineStr">
+      <c r="G115" s="11" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="H115" s="9" t="inlineStr">
+      <c r="H115" s="11" t="inlineStr">
         <is>
           <t>9/10</t>
         </is>
       </c>
-      <c r="I115" s="9" t="inlineStr">
+      <c r="I115" s="11" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="J115" s="9" t="inlineStr">
+      <c r="J115" s="11" t="inlineStr">
         <is>
           <t>让-2深盘·主胜可能不穿盘</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="9" t="n">
+      <c r="A116" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="B116" s="9" t="inlineStr">
+      <c r="B116" s="11" t="inlineStr">
         <is>
           <t>周六023</t>
         </is>
       </c>
-      <c r="C116" s="9" t="inlineStr">
+      <c r="C116" s="11" t="inlineStr">
         <is>
           <t>英超</t>
         </is>
       </c>
-      <c r="D116" s="9" t="inlineStr">
+      <c r="D116" s="11" t="inlineStr">
         <is>
           <t>曼城</t>
         </is>
       </c>
-      <c r="E116" s="9" t="inlineStr">
+      <c r="E116" s="11" t="inlineStr">
         <is>
           <t>布伦特</t>
         </is>
       </c>
-      <c r="F116" s="9" t="inlineStr">
+      <c r="F116" s="11" t="inlineStr">
         <is>
           <t>1.23/5.50/7.45</t>
         </is>
       </c>
-      <c r="G116" s="9" t="inlineStr">
+      <c r="G116" s="11" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="H116" s="9" t="inlineStr">
+      <c r="H116" s="11" t="inlineStr">
         <is>
           <t>9/10</t>
         </is>
       </c>
-      <c r="I116" s="9" t="inlineStr">
+      <c r="I116" s="11" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="J116" s="9" t="inlineStr">
+      <c r="J116" s="11" t="inlineStr">
         <is>
           <t>让-1盘</t>
         </is>
@@ -5387,7 +5387,7 @@
       </c>
       <c r="H118" s="6" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>6/10</t>
         </is>
       </c>
       <c r="I118" s="6" t="inlineStr">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="H119" s="6" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>6/10</t>
         </is>
       </c>
       <c r="I119" s="6" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="H120" s="6" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>6/10</t>
         </is>
       </c>
       <c r="I120" s="6" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="H121" s="6" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>6/10</t>
         </is>
       </c>
       <c r="I121" s="6" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="H122" s="6" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>6/10</t>
         </is>
       </c>
       <c r="I122" s="6" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="H123" s="6" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>6/10</t>
         </is>
       </c>
       <c r="I123" s="6" t="inlineStr">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="H124" s="6" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>6/10</t>
         </is>
       </c>
       <c r="I124" s="6" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="H125" s="6" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>6/10</t>
         </is>
       </c>
       <c r="I125" s="6" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="H126" s="6" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>6/10</t>
         </is>
       </c>
       <c r="I126" s="6" t="inlineStr">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="H127" s="6" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>6/10</t>
         </is>
       </c>
       <c r="I127" s="6" t="inlineStr">
@@ -5857,27 +5857,27 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>周六001</t>
+          <t>周六002</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>澳超</t>
+          <t>日职</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>奥克兰FC</t>
+          <t>大阪樱花</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
         <is>
-          <t>阿德莱德</t>
+          <t>长崎航海</t>
         </is>
       </c>
       <c r="F128" s="6" t="inlineStr">
         <is>
-          <t>1.98/3.15/3.26</t>
+          <t>1.56/3.75/4.50</t>
         </is>
       </c>
       <c r="G128" s="6" t="inlineStr">
@@ -5932,42 +5932,42 @@
     <row r="135">
       <c r="A135" s="14" t="inlineStr">
         <is>
-          <t>⬜ 周六005 波鸿vs汉诺威96 → 客胜/平局 (信心7/10)</t>
+          <t>⬜ 周六005 波鸿vs汉诺威96 → 客胜/平局 (信心6/10)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="14" t="inlineStr">
         <is>
-          <t>⬜ 周六006 利物浦vs切尔西 → 主胜/平局 (信心7/10)</t>
+          <t>⬜ 周六006 利物浦vs切尔西 → 主胜/平局 (信心6/10)</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="14" t="inlineStr">
         <is>
-          <t>⬜ 周六009 萨普斯堡vs腓特烈 → 主胜/平局 (信心7/10)</t>
+          <t>⬜ 周六009 萨普斯堡vs腓特烈 → 主胜/平局 (信心6/10)</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="14" t="inlineStr">
         <is>
-          <t>⬜ 周六012 代格福什vs米亚尔比 → 客胜/平局 (信心7/10)</t>
+          <t>⬜ 周六012 代格福什vs米亚尔比 → 客胜/平局 (信心6/10)</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="14" t="inlineStr">
         <is>
-          <t>⬜ 周六014 奥格斯堡vs门兴 → 主胜/平局 (信心7/10)</t>
+          <t>⬜ 周六014 奥格斯堡vs门兴 → 主胜/平局 (信心6/10)</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="14" t="inlineStr">
         <is>
-          <t>⬜ 周六018 桑德兰vs曼联 → 客胜/平局 (信心7/10)</t>
+          <t>⬜ 周六018 桑德兰vs曼联 → 客胜/平局 (信心6/10)</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6228,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="9" t="inlineStr">
+      <c r="A160" s="11" t="inlineStr">
         <is>
           <t>🟢 高信心(7/10+)</t>
         </is>
@@ -6250,7 +6250,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="9" t="inlineStr">
+      <c r="A161" s="11" t="inlineStr">
         <is>
           <t>🟢 让球SP真实数据</t>
         </is>
@@ -6272,7 +6272,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="11" t="inlineStr">
+      <c r="A162" s="9" t="inlineStr">
         <is>
           <t>🟡 平局候选</t>
         </is>
@@ -6294,7 +6294,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="11" t="inlineStr">
+      <c r="A163" s="9" t="inlineStr">
         <is>
           <t>🟡 让球数真实</t>
         </is>
@@ -6376,7 +6376,7 @@
 竞彩SP：1.98 / 3.15 / 3.26
 让球SP(真实)：3.95/3.87/1.62
 差值分析：P主=159% P平=100% P客=97%
-推荐：主胜 信心5/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(44%) 备选半全场:平胜
+推荐：主胜 信心4/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(44%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6396,7 +6396,7 @@
 竞彩SP：1.56 / 3.75 / 4.50
 让球SP(真实)：2.95/3.25/2.08
 差值分析：P主=223% P平=93% P客=77%
-推荐：主胜 信心4/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(45%) 备选半全场:平胜
+推荐：主胜 信心5/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(45%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6416,7 +6416,7 @@
 竞彩SP：5.80 / 3.95 / 1.42
 让球SP(真实)：2.46/3.25/2.41
 差值分析：P主=58% P平=85% P客=235%
-推荐：客胜 信心4/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
+推荐：客胜 信心5/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
 让球:让+1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6436,7 +6436,7 @@
 竞彩SP：1.91 / 3.00 / 3.68
 让球SP(真实)：4.32/3.35/1.67
 差值分析：P主=141% P平=90% P客=73%
-推荐：主胜 信心5/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(44%) 备选半全场:平胜
+推荐：主胜 信心4/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(44%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6456,7 +6456,7 @@
 竞彩SP：3.65 / 3.75 / 1.70
 让球SP(真实)：1.87/3.48/3.25
 差值分析：P主=98% P平=96% P客=211%
-推荐：客胜 信心7/10 比分1-2(泊松) 半全场负负 大小球大2.5(70%) 备选半全场:平负
+推荐：客胜 信心6/10 比分1-2(泊松) 半全场负负 大小球大2.5(70%) 备选半全场:平负
 让球:让+1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6476,7 +6476,7 @@
 竞彩SP：1.83 / 3.65 / 3.24
 让球SP(真实)：3.43/3.75/1.75
 差值分析：P主=199% P平=100% P客=113%
-推荐：主胜 信心7/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(70%) 备选半全场:平胜
+推荐：主胜 信心6/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(70%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6496,7 +6496,7 @@
 竞彩SP：1.99 / 3.05 / 3.35
 让球SP(真实)：4.15/3.70/1.62
 差值分析：P主=153% P平=100% P客=91%
-推荐：主胜 信心5/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(71%) 备选半全场:平胜
+推荐：主胜 信心4/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(71%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6516,7 +6516,7 @@
 竞彩SP：2.01 / 3.20 / 3.13
 让球SP(真实)：4.35/3.65/1.60
 差值分析：P主=159% P平=100% P客=102%
-推荐：主胜 信心5/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(67%) 备选半全场:负胜
+推荐：主胜 信心4/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(67%) 备选半全场:负胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6536,7 +6536,7 @@
 竞彩SP：1.83 / 3.65 / 3.24
 让球SP(真实)：3.48/3.70/1.75
 差值分析：P主=199% P平=100% P客=113%
-推荐：主胜 信心7/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(44%) 备选半全场:平胜
+推荐：主胜 信心6/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(44%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6556,7 +6556,7 @@
 竞彩SP：1.38 / 4.10 / 6.20
 让球SP(真实)：2.38/3.15/2.55
 差值分析：P主=265% P平=89% P客=59%
-推荐：主胜 信心4/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(43%) 备选半全场:平胜
+推荐：主胜 信心5/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(43%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6576,7 +6576,7 @@
 竞彩SP：2.43 / 2.70 / 2.88
 让球SP(真实)：5.95/3.90/1.42
 差值分析：P主=88% P平=79% P客=74%
-推荐：平局 信心5/10 比分2-2(泊松) 半全场负负 大小球大2.5(69%) 备选半全场:平负
+推荐：平局 信心4/10 比分2-2(泊松) 半全场负负 大小球大2.5(69%) 备选半全场:平负
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6596,7 +6596,7 @@
 竞彩SP：3.50 / 3.18 / 1.89
 让球SP(真实)：1.68/3.50/4.05
 差值分析：P主=91% P平=100% P客=168%
-推荐：客胜 信心7/10 比分0-1(泊松) 半全场平负 大小球小2.5(42%) 备选半全场:负负
+推荐：客胜 信心6/10 比分0-1(泊松) 半全场平负 大小球小2.5(42%) 备选半全场:负负
 让球:让+1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6616,7 +6616,7 @@
 竞彩SP：4.95 / 4.20 / 1.45
 让球SP(真实)：2.35/3.30/2.50
 差值分析：P主=77% P平=90% P客=262%
-推荐：客胜 信心4/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
+推荐：客胜 信心5/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
 让球:让+1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6636,7 +6636,7 @@
 竞彩SP：1.76 / 3.80 / 3.35
 让球SP(真实)：3.30/3.70/1.80
 差值分析：P主=211% P平=98% P客=111%
-推荐：主胜 信心7/10 比分3-2(泊松) 半全场负负 大小球大2.5(72%) 备选半全场:胜负
+推荐：主胜 信心6/10 比分3-2(泊松) 半全场负负 大小球大2.5(72%) 备选半全场:胜负
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6656,7 +6656,7 @@
 竞彩SP：1.32 / 4.95 / 5.90
 让球SP(真实)：1.94/3.93/2.78
 差值分析：P主=297% P平=79% P客=66%
-推荐：主胜 信心4/10 比分3-2(泊松) 半全场胜胜 大小球大2.5(72%) 备选半全场:负胜
+推荐：主胜 信心5/10 比分3-2(泊松) 半全场胜胜 大小球大2.5(72%) 备选半全场:负胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6676,7 +6676,7 @@
 竞彩SP：2.01 / 3.80 / 2.71
 让球SP(真实)：3.80/4.15/1.60
 差值分析：P主=185% P平=98% P客=137%
-推荐：主胜 信心5/10 比分3-2(泊松) 半全场负负 大小球大2.5(72%) 备选半全场:平负
+推荐：主胜 信心4/10 比分3-2(泊松) 半全场负负 大小球大2.5(72%) 备选半全场:平负
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6716,7 +6716,7 @@
 竞彩SP：3.40 / 3.40 / 1.85
 让球SP(真实)：1.72/3.80/3.52
 差值分析：P主=100% P平=100% P客=184%
-推荐：客胜 信心7/10 比分1-2(泊松) 半全场胜胜 大小球大2.5(69%) 备选半全场:负胜
+推荐：客胜 信心6/10 比分1-2(泊松) 半全场胜胜 大小球大2.5(69%) 备选半全场:负胜
 让球:让+1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6736,7 +6736,7 @@
 竞彩SP：2.68 / 3.17 / 2.27
 让球SP(真实)：1.47/4.08/4.90
 差值分析：P主=118% P平=100% P客=140%
-推荐：客胜 信心5/10 比分1-3(泊松) 半全场负负 大小球大2.5(69%) 备选半全场:平负
+推荐：客胜 信心4/10 比分1-3(泊松) 半全场负负 大小球大2.5(69%) 备选半全场:平负
 让球:让+1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6756,7 +6756,7 @@
 竞彩SP：1.80 / 2.90 / 4.40
 让球SP(真实)：3.90/3.15/1.80
 差值分析：P主=145% P平=90% P客=59%
-推荐：主胜 信心7/10 比分2-1(泊松) 半全场负负 大小球大2.5(70%) 备选半全场:平负
+推荐：主胜 信心6/10 比分2-1(泊松) 半全场负负 大小球大2.5(70%) 备选半全场:平负
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6776,7 +6776,7 @@
 竞彩SP：1.76 / 3.60 / 3.53
 让球SP(真实)：3.42/3.55/1.80
 差值分析：P主=205% P平=100% P客=102%
-推荐：主胜 信心7/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(46%) 备选半全场:平胜
+推荐：主胜 信心6/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(46%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6796,7 +6796,7 @@
 竞彩SP：3.57 / 3.30 / 1.83
 让球SP(真实)：1.73/3.70/3.56
 差值分析：P主=90% P平=97% P客=175%
-推荐：客胜 信心7/10 比分1-3(泊松) 半全场负负 大小球大2.5(70%) 备选半全场:平负
+推荐：客胜 信心6/10 比分1-3(泊松) 半全场负负 大小球大2.5(70%) 备选半全场:平负
 让球:让+1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6836,7 +6836,7 @@
 竞彩SP：4.70 / 4.95 / 1.40
 让球SP(真实)：2.44/4.10/2.10
 差值分析：P主=83% P平=79% P客=280%
-推荐：客胜 信心4/10 比分1-4(泊松) 半全场负负 大小球大2.5(73%) 备选半全场:平负
+推荐：客胜 信心5/10 比分1-4(泊松) 半全场负负 大小球大2.5(73%) 备选半全场:平负
 让球:让+1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6856,7 +6856,7 @@
 竞彩SP：1.87 / 3.35 / 3.38
 让球SP(真实)：3.76/3.50/1.73
 差值分析：P主=179% P平=100% P客=99%
-推荐：主胜 信心7/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(71%) 备选半全场:平胜
+推荐：主胜 信心6/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(71%) 备选半全场:平胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6876,7 +6876,7 @@
 竞彩SP：4.18 / 4.15 / 1.54
 让球SP(真实)：2.11/3.65/2.62
 差值分析：P主=97% P平=98% P客=263%
-推荐：客胜 信心4/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
+推荐：客胜 信心5/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
 让球:让0 无让球=— </t>
         </is>
       </c>
@@ -6916,7 +6916,7 @@
 竞彩SP：2.09 / 3.27 / 2.90
 让球SP(真实)：4.45/3.85/1.55
 差值分析：P主=145% P平=93% P客=105%
-推荐：主胜 信心5/10 比分1-0(泊松) 半全场平胜 大小球小2.5(41%) 备选半全场:胜胜
+推荐：主胜 信心4/10 比分1-0(泊松) 半全场平胜 大小球小2.5(41%) 备选半全场:胜胜
 让球:让-1 输盘=让平/让负 </t>
         </is>
       </c>
@@ -6936,7 +6936,7 @@
 竞彩SP：6.90 / 4.30 / 1.33
 让球SP(真实)：2.79/3.18/2.19
 差值分析：P主=49% P平=79% P客=255%
-推荐：客胜 信心4/10 比分1-2(泊松) 半全场负负 大小球大2.5(69%) 备选半全场:胜负
+推荐：客胜 信心5/10 比分1-2(泊松) 半全场负负 大小球大2.5(69%) 备选半全场:胜负
 让球:让+1 输盘=让平/让负 </t>
         </is>
       </c>

--- a/Aii竞彩推荐_2026-05-09.xlsx
+++ b/Aii竞彩推荐_2026-05-09.xlsx
@@ -183,11 +183,11 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -602,7 +602,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：中国竞彩网(sporttery)+500.com · 23:56</t>
+          <t>数据来源：中国竞彩网(sporttery)+500.com · 00:01</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>SP1.98/3.15/3.26 让球-1</t>
+          <t>SP1.98/3.15/3.26 让球0</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>SP1.56/3.75/4.50 让球-1</t>
+          <t>SP1.56/3.75/4.50 让球0</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>SP5.80/3.95/1.42 让球+1</t>
+          <t>SP5.80/3.95/1.42 让球0</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>SP1.91/3.00/3.68 让球-1</t>
+          <t>SP1.91/3.00/3.68 让球0</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>SP3.65/3.75/1.70 让球+1</t>
+          <t>SP3.65/3.75/1.70 让球0</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>SP1.83/3.65/3.24 让球-1</t>
+          <t>SP1.83/3.65/3.24 让球0</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>SP1.99/3.05/3.35 让球-1</t>
+          <t>SP1.99/3.05/3.35 让球0</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>SP2.01/3.20/3.13 让球-1</t>
+          <t>SP2.01/3.20/3.13 让球0</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>SP1.83/3.65/3.24 让球-1</t>
+          <t>SP1.83/3.65/3.24 让球0</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>SP1.38/4.10/6.20 让球-1</t>
+          <t>SP1.38/4.10/6.20 让球0</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>SP2.43/2.70/2.88 让球-1</t>
+          <t>SP2.43/2.70/2.88 让球0</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>SP3.50/3.18/1.89 让球+1</t>
+          <t>SP3.50/3.18/1.89 让球0</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>SP4.95/4.20/1.45 让球+1</t>
+          <t>SP4.95/4.20/1.45 让球0</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>SP1.76/3.80/3.35 让球-1</t>
+          <t>SP1.76/3.80/3.35 让球0</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>SP1.32/4.95/5.90 让球-1</t>
+          <t>SP1.32/4.95/5.90 让球0</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>SP2.01/3.80/2.71 让球-1</t>
+          <t>SP2.01/3.80/2.71 让球0</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>SP1.19/5.65/9.00 让球-2</t>
+          <t>SP1.19/5.65/9.00 让球0</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>SP3.40/3.40/1.85 让球+1</t>
+          <t>SP3.40/3.40/1.85 让球0</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>SP2.68/3.17/2.27 让球+1</t>
+          <t>SP2.68/3.17/2.27 让球0</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>SP1.80/2.90/4.40 让球-1</t>
+          <t>SP1.80/2.90/4.40 让球0</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>SP1.76/3.60/3.53 让球-1</t>
+          <t>SP1.76/3.60/3.53 让球0</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>SP3.57/3.30/1.83 让球+1</t>
+          <t>SP3.57/3.30/1.83 让球0</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>📊 竞彩SP数据（含真实让球SP · 23:56）</t>
+          <t>📊 竞彩SP数据（含真实让球SP · 00:01）</t>
         </is>
       </c>
     </row>
@@ -2170,22 +2170,22 @@
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="H45" s="6" t="inlineStr">
-        <is>
-          <t>3.95</t>
-        </is>
-      </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>3.87</t>
-        </is>
-      </c>
-      <c r="J45" s="6" t="inlineStr">
-        <is>
-          <t>1.62</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I45" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J45" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
     </row>
@@ -2216,22 +2216,22 @@
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="H46" s="7" t="inlineStr">
-        <is>
-          <t>2.95</t>
-        </is>
-      </c>
-      <c r="I46" s="7" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="J46" s="7" t="inlineStr">
-        <is>
-          <t>2.08</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I46" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J46" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
     </row>
@@ -2262,22 +2262,22 @@
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="H47" s="6" t="inlineStr">
-        <is>
-          <t>2.46</t>
-        </is>
-      </c>
-      <c r="I47" s="6" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="J47" s="6" t="inlineStr">
-        <is>
-          <t>2.41</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I47" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J47" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
     </row>
@@ -2308,22 +2308,22 @@
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="H48" s="7" t="inlineStr">
-        <is>
-          <t>4.32</t>
-        </is>
-      </c>
-      <c r="I48" s="7" t="inlineStr">
-        <is>
-          <t>3.35</t>
-        </is>
-      </c>
-      <c r="J48" s="7" t="inlineStr">
-        <is>
-          <t>1.67</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I48" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J48" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
     </row>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="H49" s="6" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="I49" s="6" t="inlineStr">
-        <is>
-          <t>3.48</t>
-        </is>
-      </c>
-      <c r="J49" s="6" t="inlineStr">
-        <is>
-          <t>3.25</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I49" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J49" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
     </row>
@@ -2400,22 +2400,22 @@
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="H50" s="7" t="inlineStr">
-        <is>
-          <t>3.43</t>
-        </is>
-      </c>
-      <c r="I50" s="7" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="J50" s="7" t="inlineStr">
-        <is>
-          <t>1.75</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I50" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J50" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
     </row>
@@ -2446,22 +2446,22 @@
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="H51" s="6" t="inlineStr">
-        <is>
-          <t>4.15</t>
-        </is>
-      </c>
-      <c r="I51" s="6" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="J51" s="6" t="inlineStr">
-        <is>
-          <t>1.62</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H51" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I51" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J51" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
     </row>
@@ -2492,22 +2492,22 @@
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="H52" s="7" t="inlineStr">
-        <is>
-          <t>4.35</t>
-        </is>
-      </c>
-      <c r="I52" s="7" t="inlineStr">
-        <is>
-          <t>3.65</t>
-        </is>
-      </c>
-      <c r="J52" s="7" t="inlineStr">
-        <is>
-          <t>1.60</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H52" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I52" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J52" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
     </row>
@@ -2538,22 +2538,22 @@
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="H53" s="6" t="inlineStr">
-        <is>
-          <t>3.48</t>
-        </is>
-      </c>
-      <c r="I53" s="6" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="J53" s="6" t="inlineStr">
-        <is>
-          <t>1.75</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H53" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I53" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J53" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
     </row>
@@ -2584,22 +2584,22 @@
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="H54" s="7" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="I54" s="7" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
-      <c r="J54" s="7" t="inlineStr">
-        <is>
-          <t>2.55</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H54" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I54" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J54" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
     </row>
@@ -2630,22 +2630,22 @@
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="H55" s="6" t="inlineStr">
-        <is>
-          <t>5.95</t>
-        </is>
-      </c>
-      <c r="I55" s="6" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="J55" s="6" t="inlineStr">
-        <is>
-          <t>1.42</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H55" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I55" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J55" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
     </row>
@@ -2676,22 +2676,22 @@
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="H56" s="7" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="I56" s="7" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="J56" s="7" t="inlineStr">
-        <is>
-          <t>4.05</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I56" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J56" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
     </row>
@@ -2722,22 +2722,22 @@
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="H57" s="6" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="I57" s="6" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="J57" s="6" t="inlineStr">
-        <is>
-          <t>2.50</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H57" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I57" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J57" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
     </row>
@@ -2768,22 +2768,22 @@
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="H58" s="7" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="I58" s="7" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="J58" s="7" t="inlineStr">
-        <is>
-          <t>1.80</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H58" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I58" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J58" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
     </row>
@@ -2814,22 +2814,22 @@
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="H59" s="6" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="I59" s="6" t="inlineStr">
-        <is>
-          <t>3.93</t>
-        </is>
-      </c>
-      <c r="J59" s="6" t="inlineStr">
-        <is>
-          <t>2.78</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H59" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I59" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J59" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
     </row>
@@ -2860,22 +2860,22 @@
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="H60" s="7" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="I60" s="7" t="inlineStr">
-        <is>
-          <t>4.15</t>
-        </is>
-      </c>
-      <c r="J60" s="7" t="inlineStr">
-        <is>
-          <t>1.60</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H60" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I60" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J60" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
     </row>
@@ -2906,22 +2906,22 @@
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="H61" s="6" t="inlineStr">
-        <is>
-          <t>2.73</t>
-        </is>
-      </c>
-      <c r="I61" s="6" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="J61" s="6" t="inlineStr">
-        <is>
-          <t>2.00</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H61" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I61" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J61" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
     </row>
@@ -2952,22 +2952,22 @@
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="H62" s="7" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="I62" s="7" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="J62" s="7" t="inlineStr">
-        <is>
-          <t>3.52</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H62" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I62" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J62" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
     </row>
@@ -2998,22 +2998,22 @@
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="H63" s="6" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="I63" s="6" t="inlineStr">
-        <is>
-          <t>4.08</t>
-        </is>
-      </c>
-      <c r="J63" s="6" t="inlineStr">
-        <is>
-          <t>4.90</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H63" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I63" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J63" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
     </row>
@@ -3044,22 +3044,22 @@
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="H64" s="7" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="I64" s="7" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
-      <c r="J64" s="7" t="inlineStr">
-        <is>
-          <t>1.80</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H64" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I64" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J64" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
     </row>
@@ -3090,22 +3090,22 @@
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="H65" s="6" t="inlineStr">
-        <is>
-          <t>3.42</t>
-        </is>
-      </c>
-      <c r="I65" s="6" t="inlineStr">
-        <is>
-          <t>3.55</t>
-        </is>
-      </c>
-      <c r="J65" s="6" t="inlineStr">
-        <is>
-          <t>1.80</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I65" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J65" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
     </row>
@@ -3136,22 +3136,22 @@
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="H66" s="7" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="I66" s="7" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="J66" s="7" t="inlineStr">
-        <is>
-          <t>3.56</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I66" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J66" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
     </row>
@@ -3628,9 +3628,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J80" s="8" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=159%P平=100%P客=97%|泊松比分1-0|半全场胜胜|大小球小2.5(44%)|让球-1=输盘/让平/让负</t>
+      <c r="J80" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=159%P平=100%P客=97%|泊松比分1-0|半全场胜胜|大小球小2.5(44%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -3680,9 +3680,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J81" s="8" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=223%P平=93%P客=77%|泊松比分2-0|半全场胜胜|大小球小2.5(45%)|让球-1=输盘/让平/让负</t>
+      <c r="J81" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=223%P平=93%P客=77%|泊松比分2-0|半全场胜胜|大小球小2.5(45%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -3732,9 +3732,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J82" s="8" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=58%P平=85%P客=235%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球+1=输盘/让平/让负</t>
+      <c r="J82" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=58%P平=85%P客=235%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -3784,9 +3784,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J83" s="8" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=141%P平=90%P客=73%|泊松比分1-0|半全场胜胜|大小球小2.5(44%)|让球-1=输盘/让平/让负</t>
+      <c r="J83" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=141%P平=90%P客=73%|泊松比分1-0|半全场胜胜|大小球小2.5(44%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -3836,9 +3836,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J84" s="8" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=98%P平=96%P客=211%|泊松比分1-2|半全场负负|大小球大2.5(70%)|让球+1=输盘/让平/让负</t>
+      <c r="J84" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=98%P平=96%P客=211%|泊松比分1-2|半全场负负|大小球大2.5(70%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -3888,9 +3888,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J85" s="8" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=199%P平=100%P客=113%|泊松比分2-1|半全场胜胜|大小球大2.5(70%)|让球-1=输盘/让平/让负</t>
+      <c r="J85" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=199%P平=100%P客=113%|泊松比分2-1|半全场胜胜|大小球大2.5(70%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -3940,9 +3940,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J86" s="8" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=153%P平=100%P客=91%|泊松比分3-1|半全场胜胜|大小球大2.5(71%)|让球-1=输盘/让平/让负</t>
+      <c r="J86" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=153%P平=100%P客=91%|泊松比分3-1|半全场胜胜|大小球大2.5(71%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -3992,9 +3992,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J87" s="8" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=159%P平=100%P客=102%|泊松比分2-1|半全场胜胜|大小球大2.5(67%)|让球-1=输盘/让平/让负</t>
+      <c r="J87" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=159%P平=100%P客=102%|泊松比分2-1|半全场胜胜|大小球大2.5(67%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -4044,9 +4044,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J88" s="8" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=199%P平=100%P客=113%|泊松比分1-0|半全场胜胜|大小球小2.5(44%)|让球-1=输盘/让平/让负</t>
+      <c r="J88" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=199%P平=100%P客=113%|泊松比分1-0|半全场胜胜|大小球小2.5(44%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -4096,61 +4096,61 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J89" s="8" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=265%P平=89%P客=59%|泊松比分2-0|半全场胜胜|大小球小2.5(43%)|让球-1=输盘/让平/让负</t>
+      <c r="J89" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=265%P平=89%P客=59%|泊松比分2-0|半全场胜胜|大小球小2.5(43%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="9" t="inlineStr">
+      <c r="A90" s="8" t="inlineStr">
         <is>
           <t>周六011</t>
         </is>
       </c>
-      <c r="B90" s="9" t="inlineStr">
+      <c r="B90" s="8" t="inlineStr">
         <is>
           <t>卡利亚里vs乌迪内斯</t>
         </is>
       </c>
-      <c r="C90" s="9" t="inlineStr">
+      <c r="C90" s="8" t="inlineStr">
         <is>
           <t>平局</t>
         </is>
       </c>
-      <c r="D90" s="9" t="inlineStr">
+      <c r="D90" s="8" t="inlineStr">
         <is>
           <t>4/10</t>
         </is>
       </c>
-      <c r="E90" s="9" t="inlineStr">
+      <c r="E90" s="8" t="inlineStr">
         <is>
           <t>2-2</t>
         </is>
       </c>
-      <c r="F90" s="9" t="inlineStr">
+      <c r="F90" s="8" t="inlineStr">
         <is>
           <t>1-2</t>
         </is>
       </c>
-      <c r="G90" s="9" t="inlineStr">
+      <c r="G90" s="8" t="inlineStr">
         <is>
           <t>负负</t>
         </is>
       </c>
-      <c r="H90" s="9" t="inlineStr">
+      <c r="H90" s="8" t="inlineStr">
         <is>
           <t>平负</t>
         </is>
       </c>
-      <c r="I90" s="9" t="inlineStr">
+      <c r="I90" s="8" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
       <c r="J90" s="10" t="inlineStr">
         <is>
-          <t>贝叶斯P主=88%P平=79%P客=74%|泊松比分2-2|半全场负负|大小球大2.5(69%)|让球-1=输盘/让平/让负|平SP低+联赛特征</t>
+          <t>贝叶斯P主=88%P平=79%P客=74%|泊松比分2-2|半全场负负|大小球大2.5(69%)|让球0=无让球/—|平SP低+联赛特征</t>
         </is>
       </c>
     </row>
@@ -4200,9 +4200,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J91" s="8" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=91%P平=100%P客=168%|泊松比分0-1|半全场平负|大小球小2.5(42%)|让球+1=输盘/让平/让负</t>
+      <c r="J91" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=91%P平=100%P客=168%|泊松比分0-1|半全场平负|大小球小2.5(42%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -4252,9 +4252,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J92" s="8" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=77%P平=90%P客=262%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球+1=输盘/让平/让负</t>
+      <c r="J92" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=77%P平=90%P客=262%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -4304,9 +4304,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J93" s="8" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=211%P平=98%P客=111%|泊松比分3-2|半全场负负|大小球大2.5(72%)|让球-1=输盘/让平/让负</t>
+      <c r="J93" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=211%P平=98%P客=111%|泊松比分3-2|半全场负负|大小球大2.5(72%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -4356,9 +4356,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J94" s="8" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=297%P平=79%P客=66%|泊松比分3-2|半全场胜胜|大小球大2.5(72%)|让球-1=输盘/让平/让负</t>
+      <c r="J94" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=297%P平=79%P客=66%|泊松比分3-2|半全场胜胜|大小球大2.5(72%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -4408,9 +4408,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J95" s="8" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=185%P平=98%P客=137%|泊松比分3-2|半全场负负|大小球大2.5(72%)|让球-1=输盘/让平/让负</t>
+      <c r="J95" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=185%P平=98%P客=137%|泊松比分3-2|半全场负负|大小球大2.5(72%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="J96" s="12" t="inlineStr">
         <is>
-          <t>贝叶斯P主=336%P平=71%P客=44%|泊松比分3-1|半全场胜胜|大小球大2.5(71%)|让球-2=输盘/让平/让负⚠️让-2深盘·主胜可能不穿盘</t>
+          <t>贝叶斯P主=336%P平=71%P客=44%|泊松比分3-1|半全场胜胜|大小球大2.5(71%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -4512,9 +4512,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J97" s="8" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=100%P平=100%P客=184%|泊松比分1-2|半全场胜胜|大小球大2.5(69%)|让球+1=输盘/让平/让负</t>
+      <c r="J97" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=100%P平=100%P客=184%|泊松比分1-2|半全场胜胜|大小球大2.5(69%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -4564,9 +4564,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J98" s="8" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=118%P平=100%P客=140%|泊松比分1-3|半全场负负|大小球大2.5(69%)|让球+1=输盘/让平/让负</t>
+      <c r="J98" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=118%P平=100%P客=140%|泊松比分1-3|半全场负负|大小球大2.5(69%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -4616,9 +4616,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J99" s="8" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=145%P平=90%P客=59%|泊松比分2-1|半全场负负|大小球大2.5(70%)|让球-1=输盘/让平/让负</t>
+      <c r="J99" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=145%P平=90%P客=59%|泊松比分2-1|半全场负负|大小球大2.5(70%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -4668,9 +4668,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J100" s="8" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=205%P平=100%P客=102%|泊松比分2-0|半全场胜胜|大小球小2.5(46%)|让球-1=输盘/让平/让负</t>
+      <c r="J100" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=205%P平=100%P客=102%|泊松比分2-0|半全场胜胜|大小球小2.5(46%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -4720,9 +4720,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J101" s="8" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=90%P平=97%P客=175%|泊松比分1-3|半全场负负|大小球大2.5(70%)|让球+1=输盘/让平/让负</t>
+      <c r="J101" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=90%P平=97%P客=175%|泊松比分1-3|半全场负负|大小球大2.5(70%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -4824,7 +4824,7 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J103" s="8" t="inlineStr">
+      <c r="J103" s="9" t="inlineStr">
         <is>
           <t>贝叶斯P主=83%P平=79%P客=280%|泊松比分1-4|半全场负负|大小球大2.5(73%)|让球+1=输盘/让平/让负</t>
         </is>
@@ -4876,7 +4876,7 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J104" s="8" t="inlineStr">
+      <c r="J104" s="9" t="inlineStr">
         <is>
           <t>贝叶斯P主=179%P平=100%P客=99%|泊松比分3-1|半全场胜胜|大小球大2.5(71%)|让球-1=输盘/让平/让负</t>
         </is>
@@ -4928,7 +4928,7 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J105" s="8" t="inlineStr">
+      <c r="J105" s="9" t="inlineStr">
         <is>
           <t>贝叶斯P主=97%P平=98%P客=263%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球0=无让球/—</t>
         </is>
@@ -5032,7 +5032,7 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J107" s="8" t="inlineStr">
+      <c r="J107" s="9" t="inlineStr">
         <is>
           <t>贝叶斯P主=145%P平=93%P客=105%|泊松比分1-0|半全场平胜|大小球小2.5(41%)|让球-1=输盘/让平/让负</t>
         </is>
@@ -5084,7 +5084,7 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J108" s="8" t="inlineStr">
+      <c r="J108" s="9" t="inlineStr">
         <is>
           <t>贝叶斯P主=49%P平=79%P客=255%|泊松比分1-2|半全场负负|大小球大2.5(69%)|让球+1=输盘/让平/让负</t>
         </is>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="J115" s="11" t="inlineStr">
         <is>
-          <t>让-2深盘·主胜可能不穿盘</t>
+          <t>无让球</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="J118" s="6" t="inlineStr">
         <is>
-          <t>让+1盘</t>
+          <t>无让球</t>
         </is>
       </c>
     </row>
@@ -5447,7 +5447,7 @@
       </c>
       <c r="J119" s="6" t="inlineStr">
         <is>
-          <t>让-1盘</t>
+          <t>无让球</t>
         </is>
       </c>
     </row>
@@ -5497,7 +5497,7 @@
       </c>
       <c r="J120" s="6" t="inlineStr">
         <is>
-          <t>让-1盘</t>
+          <t>无让球</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="J121" s="6" t="inlineStr">
         <is>
-          <t>让+1盘</t>
+          <t>无让球</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
-          <t>让-1盘</t>
+          <t>无让球</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="J123" s="6" t="inlineStr">
         <is>
-          <t>让+1盘</t>
+          <t>无让球</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="J124" s="6" t="inlineStr">
         <is>
-          <t>让-1盘</t>
+          <t>无让球</t>
         </is>
       </c>
     </row>
@@ -5747,7 +5747,7 @@
       </c>
       <c r="J125" s="6" t="inlineStr">
         <is>
-          <t>让-1盘</t>
+          <t>无让球</t>
         </is>
       </c>
     </row>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="J126" s="6" t="inlineStr">
         <is>
-          <t>让+1盘</t>
+          <t>无让球</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="J128" s="6" t="inlineStr">
         <is>
-          <t>让-1盘</t>
+          <t>无让球</t>
         </is>
       </c>
     </row>
@@ -6019,7 +6019,7 @@
           <t>周六017+周六023</t>
         </is>
       </c>
-      <c r="C150" s="8" t="inlineStr">
+      <c r="C150" s="9" t="inlineStr">
         <is>
           <t>·莱红牛:主胜(1.19)
 ·曼城:主胜(1.23)</t>
@@ -6055,7 +6055,7 @@
           <t>周六017+周六023+周六027</t>
         </is>
       </c>
-      <c r="C151" s="8" t="inlineStr">
+      <c r="C151" s="9" t="inlineStr">
         <is>
           <t>·莱红牛:主胜(1.19)
 ·曼城:主胜(1.23)
@@ -6092,7 +6092,7 @@
           <t>周六017+周六023+周六027+周六005</t>
         </is>
       </c>
-      <c r="C152" s="8" t="inlineStr">
+      <c r="C152" s="9" t="inlineStr">
         <is>
           <t>·莱红牛:主胜(1.19)
 ·曼城:主胜(1.23)
@@ -6130,7 +6130,7 @@
           <t>周六017+周六023+周六027+周六005+周六006</t>
         </is>
       </c>
-      <c r="C153" s="8" t="inlineStr">
+      <c r="C153" s="9" t="inlineStr">
         <is>
           <t>·莱红牛:主胜(1.19)
 ·曼城:主胜(1.23)
@@ -6169,7 +6169,7 @@
           <t>周六017+周六023+周六027+周六005+周六006+周六009</t>
         </is>
       </c>
-      <c r="C154" s="8" t="inlineStr">
+      <c r="C154" s="9" t="inlineStr">
         <is>
           <t>·莱红牛:主胜(1.19)
 ·曼城:主胜(1.23)
@@ -6272,7 +6272,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="9" t="inlineStr">
+      <c r="A162" s="8" t="inlineStr">
         <is>
           <t>🟡 平局候选</t>
         </is>
@@ -6294,7 +6294,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="9" t="inlineStr">
+      <c r="A163" s="8" t="inlineStr">
         <is>
           <t>🟡 让球数真实</t>
         </is>
@@ -6374,10 +6374,10 @@
           <t xml:space="preserve">时间：14:00
 联赛：澳超
 竞彩SP：1.98 / 3.15 / 3.26
-让球SP(真实)：3.95/3.87/1.62
+让球SP(真实)：暂无
 差值分析：P主=159% P平=100% P客=97%
 推荐：主胜 信心4/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(44%) 备选半全场:平胜
-让球:让-1 输盘=让平/让负 </t>
+让球:让0 无让球=— </t>
         </is>
       </c>
     </row>
@@ -6394,10 +6394,10 @@
           <t xml:space="preserve">时间：15:00
 联赛：日职
 竞彩SP：1.56 / 3.75 / 4.50
-让球SP(真实)：2.95/3.25/2.08
+让球SP(真实)：暂无
 差值分析：P主=223% P平=93% P客=77%
 推荐：主胜 信心5/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(45%) 备选半全场:平胜
-让球:让-1 输盘=让平/让负 </t>
+让球:让0 无让球=— </t>
         </is>
       </c>
     </row>
@@ -6414,10 +6414,10 @@
           <t xml:space="preserve">时间：15:30
 联赛：韩职
 竞彩SP：5.80 / 3.95 / 1.42
-让球SP(真实)：2.46/3.25/2.41
+让球SP(真实)：暂无
 差值分析：P主=58% P平=85% P客=235%
 推荐：客胜 信心5/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
-让球:让+1 输盘=让平/让负 </t>
+让球:让0 无让球=— </t>
         </is>
       </c>
     </row>
@@ -6434,10 +6434,10 @@
           <t xml:space="preserve">时间：18:00
 联赛：韩职
 竞彩SP：1.91 / 3.00 / 3.68
-让球SP(真实)：4.32/3.35/1.67
+让球SP(真实)：暂无
 差值分析：P主=141% P平=90% P客=73%
 推荐：主胜 信心4/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(44%) 备选半全场:平胜
-让球:让-1 输盘=让平/让负 </t>
+让球:让0 无让球=— </t>
         </is>
       </c>
     </row>
@@ -6454,10 +6454,10 @@
           <t xml:space="preserve">时间：19:00
 联赛：德乙
 竞彩SP：3.65 / 3.75 / 1.70
-让球SP(真实)：1.87/3.48/3.25
+让球SP(真实)：暂无
 差值分析：P主=98% P平=96% P客=211%
 推荐：客胜 信心6/10 比分1-2(泊松) 半全场负负 大小球大2.5(70%) 备选半全场:平负
-让球:让+1 输盘=让平/让负 </t>
+让球:让0 无让球=— </t>
         </is>
       </c>
     </row>
@@ -6474,10 +6474,10 @@
           <t xml:space="preserve">时间：19:30
 联赛：英超
 竞彩SP：1.83 / 3.65 / 3.24
-让球SP(真实)：3.43/3.75/1.75
+让球SP(真实)：暂无
 差值分析：P主=199% P平=100% P客=113%
 推荐：主胜 信心6/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(70%) 备选半全场:平胜
-让球:让-1 输盘=让平/让负 </t>
+让球:让0 无让球=— </t>
         </is>
       </c>
     </row>
@@ -6494,10 +6494,10 @@
           <t xml:space="preserve">时间：19:30
 联赛：英冠
 竞彩SP：1.99 / 3.05 / 3.35
-让球SP(真实)：4.15/3.70/1.62
+让球SP(真实)：暂无
 差值分析：P主=153% P平=100% P客=91%
 推荐：主胜 信心4/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(71%) 备选半全场:平胜
-让球:让-1 输盘=让平/让负 </t>
+让球:让0 无让球=— </t>
         </is>
       </c>
     </row>
@@ -6514,10 +6514,10 @@
           <t xml:space="preserve">时间：20:00
 联赛：西甲
 竞彩SP：2.01 / 3.20 / 3.13
-让球SP(真实)：4.35/3.65/1.60
+让球SP(真实)：暂无
 差值分析：P主=159% P平=100% P客=102%
 推荐：主胜 信心4/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(67%) 备选半全场:负胜
-让球:让-1 输盘=让平/让负 </t>
+让球:让0 无让球=— </t>
         </is>
       </c>
     </row>
@@ -6534,10 +6534,10 @@
           <t xml:space="preserve">时间：20:00
 联赛：挪超
 竞彩SP：1.83 / 3.65 / 3.24
-让球SP(真实)：3.48/3.70/1.75
+让球SP(真实)：暂无
 差值分析：P主=199% P平=100% P客=113%
 推荐：主胜 信心6/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(44%) 备选半全场:平胜
-让球:让-1 输盘=让平/让负 </t>
+让球:让0 无让球=— </t>
         </is>
       </c>
     </row>
@@ -6554,10 +6554,10 @@
           <t xml:space="preserve">时间：20:00
 联赛：芬超
 竞彩SP：1.38 / 4.10 / 6.20
-让球SP(真实)：2.38/3.15/2.55
+让球SP(真实)：暂无
 差值分析：P主=265% P平=89% P客=59%
 推荐：主胜 信心5/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(43%) 备选半全场:平胜
-让球:让-1 输盘=让平/让负 </t>
+让球:让0 无让球=— </t>
         </is>
       </c>
     </row>
@@ -6574,10 +6574,10 @@
           <t xml:space="preserve">时间：21:00
 联赛：意甲
 竞彩SP：2.43 / 2.70 / 2.88
-让球SP(真实)：5.95/3.90/1.42
+让球SP(真实)：暂无
 差值分析：P主=88% P平=79% P客=74%
 推荐：平局 信心4/10 比分2-2(泊松) 半全场负负 大小球大2.5(69%) 备选半全场:平负
-让球:让-1 输盘=让平/让负 </t>
+让球:让0 无让球=— </t>
         </is>
       </c>
     </row>
@@ -6594,10 +6594,10 @@
           <t xml:space="preserve">时间：21:00
 联赛：瑞超
 竞彩SP：3.50 / 3.18 / 1.89
-让球SP(真实)：1.68/3.50/4.05
+让球SP(真实)：暂无
 差值分析：P主=91% P平=100% P客=168%
 推荐：客胜 信心6/10 比分0-1(泊松) 半全场平负 大小球小2.5(42%) 备选半全场:负负
-让球:让+1 输盘=让平/让负 </t>
+让球:让0 无让球=— </t>
         </is>
       </c>
     </row>
@@ -6614,10 +6614,10 @@
           <t xml:space="preserve">时间：21:00
 联赛：瑞超
 竞彩SP：4.95 / 4.20 / 1.45
-让球SP(真实)：2.35/3.30/2.50
+让球SP(真实)：暂无
 差值分析：P主=77% P平=90% P客=262%
 推荐：客胜 信心5/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
-让球:让+1 输盘=让平/让负 </t>
+让球:让0 无让球=— </t>
         </is>
       </c>
     </row>
@@ -6634,10 +6634,10 @@
           <t xml:space="preserve">时间：21:30
 联赛：德甲
 竞彩SP：1.76 / 3.80 / 3.35
-让球SP(真实)：3.30/3.70/1.80
+让球SP(真实)：暂无
 差值分析：P主=211% P平=98% P客=111%
 推荐：主胜 信心6/10 比分3-2(泊松) 半全场负负 大小球大2.5(72%) 备选半全场:胜负
-让球:让-1 输盘=让平/让负 </t>
+让球:让0 无让球=— </t>
         </is>
       </c>
     </row>
@@ -6654,10 +6654,10 @@
           <t xml:space="preserve">时间：21:30
 联赛：德甲
 竞彩SP：1.32 / 4.95 / 5.90
-让球SP(真实)：1.94/3.93/2.78
+让球SP(真实)：暂无
 差值分析：P主=297% P平=79% P客=66%
 推荐：主胜 信心5/10 比分3-2(泊松) 半全场胜胜 大小球大2.5(72%) 备选半全场:负胜
-让球:让-1 输盘=让平/让负 </t>
+让球:让0 无让球=— </t>
         </is>
       </c>
     </row>
@@ -6674,10 +6674,10 @@
           <t xml:space="preserve">时间：21:30
 联赛：德甲
 竞彩SP：2.01 / 3.80 / 2.71
-让球SP(真实)：3.80/4.15/1.60
+让球SP(真实)：暂无
 差值分析：P主=185% P平=98% P客=137%
 推荐：主胜 信心4/10 比分3-2(泊松) 半全场负负 大小球大2.5(72%) 备选半全场:平负
-让球:让-1 输盘=让平/让负 </t>
+让球:让0 无让球=— </t>
         </is>
       </c>
     </row>
@@ -6691,13 +6691,13 @@
     <row r="132" ht="130" customHeight="1">
       <c r="B132" s="17" t="inlineStr">
         <is>
-          <t>时间：21:30
+          <t xml:space="preserve">时间：21:30
 联赛：德甲
 竞彩SP：1.19 / 5.65 / 9.00
-让球SP(真实)：2.73/3.80/2.00
+让球SP(真实)：暂无
 差值分析：P主=336% P平=71% P客=44%
 推荐：主胜 信心9/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(71%) 备选半全场:平胜
-让球:让-2 输盘=让平/让负 让-2深盘·主胜可能不穿盘</t>
+让球:让0 无让球=— </t>
         </is>
       </c>
     </row>
@@ -6714,10 +6714,10 @@
           <t xml:space="preserve">时间：22:00
 联赛：英超
 竞彩SP：3.40 / 3.40 / 1.85
-让球SP(真实)：1.72/3.80/3.52
+让球SP(真实)：暂无
 差值分析：P主=100% P平=100% P客=184%
 推荐：客胜 信心6/10 比分1-2(泊松) 半全场胜胜 大小球大2.5(69%) 备选半全场:负胜
-让球:让+1 输盘=让平/让负 </t>
+让球:让0 无让球=— </t>
         </is>
       </c>
     </row>
@@ -6734,10 +6734,10 @@
           <t xml:space="preserve">时间：22:00
 联赛：英超
 竞彩SP：2.68 / 3.17 / 2.27
-让球SP(真实)：1.47/4.08/4.90
+让球SP(真实)：暂无
 差值分析：P主=118% P平=100% P客=140%
 推荐：客胜 信心4/10 比分1-3(泊松) 半全场负负 大小球大2.5(69%) 备选半全场:平负
-让球:让+1 输盘=让平/让负 </t>
+让球:让0 无让球=— </t>
         </is>
       </c>
     </row>
@@ -6754,10 +6754,10 @@
           <t xml:space="preserve">时间：22:15
 联赛：西甲
 竞彩SP：1.80 / 2.90 / 4.40
-让球SP(真实)：3.90/3.15/1.80
+让球SP(真实)：暂无
 差值分析：P主=145% P平=90% P客=59%
 推荐：主胜 信心6/10 比分2-1(泊松) 半全场负负 大小球大2.5(70%) 备选半全场:平负
-让球:让-1 输盘=让平/让负 </t>
+让球:让0 无让球=— </t>
         </is>
       </c>
     </row>
@@ -6774,10 +6774,10 @@
           <t xml:space="preserve">时间：22:30
 联赛：荷乙
 竞彩SP：1.76 / 3.60 / 3.53
-让球SP(真实)：3.42/3.55/1.80
+让球SP(真实)：暂无
 差值分析：P主=205% P平=100% P客=102%
 推荐：主胜 信心6/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(46%) 备选半全场:平胜
-让球:让-1 输盘=让平/让负 </t>
+让球:让0 无让球=— </t>
         </is>
       </c>
     </row>
@@ -6794,10 +6794,10 @@
           <t xml:space="preserve">时间：00:00
 联赛：意甲
 竞彩SP：3.57 / 3.30 / 1.83
-让球SP(真实)：1.73/3.70/3.56
+让球SP(真实)：暂无
 差值分析：P主=90% P平=97% P客=175%
 推荐：客胜 信心6/10 比分1-3(泊松) 半全场负负 大小球大2.5(70%) 备选半全场:平负
-让球:让+1 输盘=让平/让负 </t>
+让球:让0 无让球=— </t>
         </is>
       </c>
     </row>
@@ -7085,7 +7085,7 @@
           <t>周六017+周六023</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>·莱红牛:主胜(1.19)
 ·曼城:主胜(1.23)</t>
@@ -7121,7 +7121,7 @@
           <t>周六017+周六023+周六027</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>·莱红牛:主胜(1.19)
 ·曼城:主胜(1.23)
@@ -7158,7 +7158,7 @@
           <t>周六017+周六023+周六027+周六005</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>·莱红牛:主胜(1.19)
 ·曼城:主胜(1.23)
@@ -7196,7 +7196,7 @@
           <t>周六017+周六023+周六027+周六005+周六006</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>·莱红牛:主胜(1.19)
 ·曼城:主胜(1.23)
@@ -7235,7 +7235,7 @@
           <t>周六017+周六023+周六027+周六005+周六006+周六009</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>·莱红牛:主胜(1.19)
 ·曼城:主胜(1.23)
@@ -7287,7 +7287,7 @@
           <t>周六017+周六023</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>·莱红牛:3-1(6.0)
 ·曼城:4-1(6.2)</t>
@@ -7328,7 +7328,7 @@
           <t>周六017+周六023+周六027</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>·莱红牛:3-1(6.0)
 ·曼城:4-1(6.2)
@@ -7384,9 +7384,9 @@
           <t>周六017+周六023+周六027</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>·莱红牛:主胜(1.19)/让平/让负
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>·莱红牛:主胜(1.19)/—
 ·曼城:主胜(1.23)/让平/让负
 ·迈季宽广:客胜(1.26)/—</t>
         </is>
@@ -7426,12 +7426,12 @@
           <t>周六017+周六023+周六027+周六005</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>·莱红牛:主胜(1.19)/让平/让负
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>·莱红牛:主胜(1.19)/—
 ·曼城:主胜(1.23)/让平/让负
 ·迈季宽广:客胜(1.26)/—
-·波鸿:客胜(1.70)/让平/让负</t>
+·波鸿:客胜(1.70)/—</t>
         </is>
       </c>
       <c r="E14" s="6" t="n">
@@ -7483,7 +7483,7 @@
           <t>周六017+周六023</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>·莱红牛:胜胜(2.2)
 ·曼城:胜胜(2.2)</t>
@@ -7524,7 +7524,7 @@
           <t>周六017+周六023+周六027</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>·莱红牛:胜胜(2.2)
 ·曼城:胜胜(2.2)
@@ -7566,7 +7566,7 @@
           <t>周六017+周六023+周六027+周六005</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>·莱红牛:胜胜(2.2)
 ·曼城:胜胜(2.2)
@@ -7609,7 +7609,7 @@
           <t>周六017+周六023+周六027+周六005+周六006</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>·莱红牛:胜胜(2.2)
 ·曼城:胜胜(2.2)
@@ -7653,7 +7653,7 @@
           <t>周六017+周六023+周六027+周六005+周六006+周六009</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>·莱红牛:胜胜(2.2)
 ·曼城:胜胜(2.2)

--- a/Aii竞彩推荐_2026-05-09.xlsx
+++ b/Aii竞彩推荐_2026-05-09.xlsx
@@ -602,7 +602,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：中国竞彩网(sporttery)+500.com · 00:01</t>
+          <t>数据来源：中国竞彩网(sporttery)+500.com · 00:10</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>📊 竞彩SP数据（含真实让球SP · 00:01）</t>
+          <t>📊 竞彩SP数据（含真实让球SP · 00:10）</t>
         </is>
       </c>
     </row>

--- a/Aii竞彩推荐_2026-05-09.xlsx
+++ b/Aii竞彩推荐_2026-05-09.xlsx
@@ -602,7 +602,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：中国竞彩网(sporttery)+500.com · 00:10</t>
+          <t>数据来源：中国竞彩网(sporttery)+500.com · 00:18</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>📊 竞彩SP数据（含真实让球SP · 00:10）</t>
+          <t>📊 竞彩SP数据（含真实让球SP · 00:18）</t>
         </is>
       </c>
     </row>
